--- a/assets/xlsx/Re Testing.xlsx
+++ b/assets/xlsx/Re Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMG\Documents\GITHUB\automationtestingjudges\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A590573D-5483-4FAB-BB12-AD60997C3DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB3B5D6-6F4E-4AAA-ADE0-A7738BA7CA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
   <si>
     <t>No</t>
   </si>
@@ -34,20 +34,9 @@
     <t>Context</t>
   </si>
   <si>
-    <t>Apakah voicebot bisa diintegrasikan dengan:
-Telephony system (PSTN, SIP, Twilio, Genesys, Avaya, dll.)
-WhatsApp/Telegram call, WebRTC, atau aplikasi mobile
-CRM/ERP/Helpdesk (Salesforce, Zendesk, HubSpot, dll.)</t>
-  </si>
-  <si>
     <t>Voicebot Botika dapat diintegrasikan di media atau platform apa pun selama platform tersebut mendukung fitur voicebot atau komunikasi suara.
 Integrasi bisa dilakukan melalui API atau gateway, baik untuk sistem telephony (seperti SIP dan softphone), platform digital (seperti WhatsApp Call, WebRTC, atau mobile app), maupun sistem bisnis internal seperti CRM atau ERP.
 Dengan fleksibilitas ini, voicebot dapat beroperasi di berbagai lingkungan sesuai kebutuhan pengguna.</t>
-  </si>
-  <si>
-    <t>Apakah ada dashboard reporting (jumlah call, success rate, intent coverage)?
-Metrics apa saja yang disediakan: average handling time, call drop rate, escalation rate?
-Apakah raw conversation log bisa di-export untuk analisis sendiri?</t>
   </si>
   <si>
     <t>Terdapat detail repot sbb pada dashboard voicebotika
@@ -85,17 +74,9 @@
 API ini membantu memantau performa kampanye dan insight perilaku pengguna secara real-time maupun historis.</t>
   </si>
   <si>
-    <t>Use case VoiceBot untuk penagihan pembayaran:
-Contoh: VoiceBot menghubungi pelanggan terkait pembayaran, namun pelanggan baru akan membayarkan di minggu depan.
-Apakah sistem dapat menyimpan data pelanggan dan jadwal pembayaran di dalam reporting VoiceBot? (Category/Tagging)</t>
-  </si>
-  <si>
     <t>Bisa, namun memerlukan custom khusus.
 Voicebot dapat dikembangkan untuk menyimpan data pelanggan dan jadwal pembayaran, termasuk mencatat status interaksi dan informasi penting lainnya.
 Melalui penyesuaian ini, data dapat diatur menggunakan kategori atau tagging agar mudah digunakan untuk pelaporan dan analisis lanjutan.</t>
-  </si>
-  <si>
-    <t>Konfirmasi apakah *VoiceBot sudah menggunakan teknologi Generative AI, dan apakah dapat **terhubung ke payment gateway* (contoh: pemesanan makanan hingga pembayaran).</t>
   </si>
   <si>
     <t>Hal tersebut bisa dilakukan, karena Botika sudah menggunakan teknologi Agentic AI yang mampu memahami konteks percakapan dan mengeksekusi tindakan secara proaktif.
@@ -104,15 +85,9 @@
 Oleh karena itu, penerapan fitur ini belum efisien untuk dilakukan dalam skenario voice interaction saat ini.</t>
   </si>
   <si>
-    <t>Apakah untuk VoiceBot ini sudah tersedia *sentiment analytics*? Jikalau belum apakah bisa di Custom?</t>
-  </si>
-  <si>
     <t>Hal tersebut sudah tersedia. Bahkan, jika ada kebutuhan untuk open API, fitur tersebut juga sudah disiapkan dan bisa diintegrasikan sesuai kebutuhan sistem kamu.
 Kalau kamu ingin tahu lebih detail soal implementasinya, kamu bisa langsung hubungi tim support Botika di support@botika.online
 .</t>
-  </si>
-  <si>
-    <t>Jika terdapat beberapa skenario, berapa banyak agent yang perlu dibuat?</t>
   </si>
   <si>
     <t>Jumlah agent bergantung pada kompleksitas journey.
@@ -121,160 +96,26 @@
 Selain itu, juga terdapat fitur eskalasi otomatis ke agent manusia ketika voicebot tidak dapat menangani percakapan tertentu.</t>
   </si>
   <si>
-    <t>Bagaimana jika panggilan masuk ke voice mail, apakah akan tercatat sebagai call yang masuk atau tidak? Mengingat voice mail setiap provider bisa berbeda-beda</t>
-  </si>
-  <si>
-    <t>Jika panggilan masuk diarahkan ke voice mail, tetap akan tercatat sebagai panggilan masuk/berhasil di sistem. Hal ini karena dari sisi koneksi telepon, panggilan sudah terhubung ke nomor tujuan, sehingga sistem mengenalinya sebagai panggilan yang berhasil.</t>
-  </si>
-  <si>
-    <t>Berapa lama waktu yang dibutuhkan untuk set integrasi call (SIP Integration) di Ailoov?</t>
-  </si>
-  <si>
-    <t>Proses integrasi SIP umumnya memakan waktu sekitar 5 hari kerja, dengan pelaksanaan bersama tim SIP provider yang digunakan oleh client. Durasi ini dapat lebih cepat atau lebih lama, tergantung pada intensitas diskusi dan koordinasi teknis yang dilakukan selama proses integrasi berlangsung.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apakah platform ailoov bisa diintegrasikan ke API milik client? 
-</t>
-  </si>
-  <si>
     <t>Hal tersebut bisa dilakukan, dan Voicebotika juga telah menyediakan Open API untuk mendukung integrasi dengan sistem eksternal.
 Selama API milik client memiliki endpoint dan dokumentasi yang sesuai, proses integrasi dapat dilakukan dengan penyesuaian teknis agar kedua sistem dapat saling berkomunikasi dengan baik, misalnya untuk verifikasi data, sinkronisasi informasi, atau eksekusi fungsi tertentu.</t>
-  </si>
-  <si>
-    <t>Apakah ada mekanisme retry call jika user tidak menjawab call atau pada konidisi tertentu?</t>
-  </si>
-  <si>
-    <t>Mekanisme retry atau redial pada Voicebot dapat diatur secara fleksibel sesuai kebutuhan. Misalnya, jika panggilan pertama tidak dijawab atau user merespons “lagi sibuk, telepon lagi nanti”, sistem bisa dijadwalkan untuk melakukan recall dengan jeda waktu yang dapat disesuaikan.
-Pengaturan redial ini dapat dikustomisasi sepenuhnya melalui API Voicebot, termasuk frekuensi, interval, dan kondisi panggilan ulang sesuai skenario bisnis. Jika kamu ingin mencoba API voicebot lebih lanjut, silakan hubungi galuh@botika.online</t>
-  </si>
-  <si>
-    <t>Jika call masuk ke voicemail apakah bisa di flagging dan apakah akan masuk ke tagihan?</t>
-  </si>
-  <si>
-    <t>Jika panggilan masuk diarahkan ke voicemail, sistem tetap akan mencatatnya sebagai panggilan masuk atau panggilan berhasil, karena dari sisi teknis, koneksi antara sistem Voicebot dan jaringan telepon telah tersambung dengan sukses. Artinya, walaupun tidak ada interaksi langsung dengan penerima, status panggilan dianggap berhasil karena provider telekomunikasi telah mengonfirmasi koneksi ke nomor tujuan.
-Dengan demikian, sistem mendeteksi panggilan tersebut sebagai call connected, dan data seperti durasi panggilan serta status koneksi tetap akan direkam di dashboard untuk kebutuhan monitoring maupun perhitungan tagihan.</t>
-  </si>
-  <si>
-    <t>Jika client ingin melihat percakapan yang terjadi antara agent dengan user, apakah bisa dibuatkan transcript call berupa bubble agent, bot dan user layaknya chat console monitoring?</t>
   </si>
   <si>
     <t>Transkrip call sudah tersedia pada fitur broadcast call di voicebotika. client dapat mengaskes transkrip panggilan antara agent dan pengguna. perlu diperhatikan, yang ditampilkan adalah transkrip call bukan chat console.</t>
   </si>
   <si>
-    <t>Jika terdapat banyak scenario dengan 1 persona Agent yang sama, apakah bisa dilakukan cloning agent?</t>
-  </si>
-  <si>
     <t>Fitur ini tersedia untuk mempermudah pengguna dalam menduplikasi sebuah agent. Proses cloning agent kini dapat dilakukan langsung oleh user yang memegang credential akun dashboard (PIC). Jadi, jika Anda perlu mengatur banyak skenario menggunakan satu persona agent yang sama, Anda dapat melakukannya secara mandiri melalui dashboard.</t>
-  </si>
-  <si>
-    <t>VB ini apakah support untuk memberika backup promotion? 
-Sebagai contoh : 
-(diluar scenario sudah terdapat list wording untuk promosi beberapa produk yang nanti dipilih sama client untuk dijalankan scenarionya) 
-VB sudah memberika promosi terkait {Produk 1} dan user tidak tertarik dengan produknya. Lalu VB bertanya terlebih dahulu user ini sedang bekerja/punya usaha, nanti penawaran pada {produk 2} dapat menyesuaikan dari jenis kondisi user(bekerja/pengusaha/mahasiswa), seperti harga, bundling, membership</t>
   </si>
   <si>
     <t>Fitur ini dapat dilakukan dengan penyesuaian pada Journey dan persona agent. Voicebot dapat memberikan interaksi dan penawaran yang personalized berdasarkan kondisi atau respons pengguna, sehingga skenario percakapan dapat disesuaikan untuk berbagai kebutuhan.</t>
   </si>
   <si>
-    <t>Pada Dashboard ailoovkan terdapat upload RAG, kalau dokumennya adalah pdf dan dalam pdf itu terdapat image yang penuh Text, apakah bisa dilakukan OCR?</t>
-  </si>
-  <si>
-    <t>Fitur ini dapat dilakukan dengan teknologi OCR (Optical Character Recognition), yang memungkinkan ekstraksi teks dari gambar dalam dokumen PDF. Kualitas hasil ekstraksi bergantung pada kejelasan dan resolusi gambar, sehingga pastikan gambar cukup jelas agar proses berjalan efektif.</t>
-  </si>
-  <si>
-    <t>Jika user salah ngomong (contoh: “1997… eh maksud nya 98”), apakah event correction itu bisa terekam di reporting, atau hanya hasil akhir yang disimpan? 
-terutama waktu pengucapan pertama iya menyebutkan full kata "1997" cuman waktu koreksi hanya"maksud nya 98"</t>
-  </si>
-  <si>
     <t>Voicebotika menyimpan transkrip dan hasil dalam bentuk summary, sehingga pengguna dapat melihat seluruh percakapan sekaligus output akhirnya, memudahkan analisis dan evaluasi performa agent.</t>
-  </si>
-  <si>
-    <t>Hasil VB ini apakah bisa dikirim bersamaan dengan file recording melalui API ke sistem Client?</t>
-  </si>
-  <si>
-    <t>Hal tersebut bisa dilakukan. Untuk informasi lebih lanjut mengenai pengiriman hasil Voicebotika beserta file recording melalui API ke sistem klien, Anda dapat menghubungi support@botika.online.</t>
-  </si>
-  <si>
-    <t>Sejauh mana Persona dari VB ini bisa diatur? alur/nada ucapannya bisa dicustomisasi perscenario yang diucapkan 
-Contoh : Jadi diawal VB profiling dlu apakah usernya ini orang tua/anak muda? jadi alur/nada ucapannya disesuaikan dengan user</t>
   </si>
   <si>
     <t>Terkait persona dan kompleksitas Voicebot, semua dapat diatur melalui dashboard Voicebot dengan metode prompting, menyesuaikan persona dan flow berdasarkan user journey. Dengan cara ini, skenario percakapan bisa dibuat untuk satu agent maupun lebih, termasuk penyesuaian alur dan nada ucapan per skenario. Misalnya, di awal percakapan Voicebotika bisa melakukan profiling untuk mengetahui apakah pengguna orang tua atau anak muda, sehingga alur dan nada ucapannya dapat disesuaikan dengan karakteristik pengguna tersebut.</t>
   </si>
   <si>
     <t>KB Ailoov</t>
-  </si>
-  <si>
-    <t>Apa saja fitur Platform v3?</t>
-  </si>
-  <si>
-    <t>Platform V3 dilengkapi dengan 4 fitur utama, yaitu : 
-- Persona, Fitur ini memungkinkan Anda mengatur karakter dan gaya percakapan chatbot. Dengan begitu, chatbot dapat memiliki kepribadian unik, misalnya ramah, formal, atau santai sehingga lebih sesuai dengan audiens yang berinteraksi dengannya. 
-- Knowledge Base, Ini adalah tempat penyimpanan informasi yang akan digunakan chatbot untuk menjawab pertanyaan pengguna. Singkatnya, ini seperti “otak” pada chatbot anda.
-- Chat Console, Melalui fitur ini, anda bisa memantau dan mengelola percakapan secara langsung antara chatbot dan pengguna. Jadi, anda bisa memastikan semua interaksi berjalan lancar dan memberikan pengalaman terbaik bagi pengguna.
-- Integration, Fitur ini memungkinkan chatbot anda terhubung ke berbagai platform seperti Webchat, Telegram, WhatsApp Business Solution (WABIS), Line, Viber, atau sistem lain melalui Webhook/API. Dengan integrasi ini, chatbot bisa diakses di banyak channel sekaligus, sehingga lebih mudah dijangkau oleh pengguna.</t>
-  </si>
-  <si>
-    <t>Apa yang dimaksud dengan fitur persona di platform v3?</t>
-  </si>
-  <si>
-    <t>Fitur Persona adalah pengaturan karakter dan gaya berbicara chatbot. Dengan fitur ini, chatbot tidak hanya memberikan jawaban, tetapi juga punya “kepribadian” tertentu yang bisa disesuaikan dengan kebutuhan.</t>
-  </si>
-  <si>
-    <t>Informasi apa saja yang bisa dimasukkan ke dalam Knowledge Base?</t>
-  </si>
-  <si>
-    <t>Segala hal yang sering ditanyakan pengguna, misalnya: jam operasional perusahaan, daftar produk, cara mendaftar layanan, harga barang, hingga FAQ (Frequently Asked Questions).</t>
-  </si>
-  <si>
-    <t>Apakah halaman Demo selalu muncul setiap login?</t>
-  </si>
-  <si>
-    <t>Tidak, halaman Demo hanya muncul pertama kali saat akun baru dibuat.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara langsung masuk ke dashboard tanpa Demo pada platform v3?</t>
-  </si>
-  <si>
-    <t>Jika Anda sudah memiliki akun, saat masuk kembali Anda akan langsung diarahkan ke halaman utama (dashboard) untuk dapat menggunakan beberapa fitur yang tersedia.</t>
-  </si>
-  <si>
-    <t>Apa yang dimaksud dengan caption widget?</t>
-  </si>
-  <si>
-    <t>Caption Widget menampilkan teks sambutan di widget webchat, misalnya 'Hello, can I help you?'.</t>
-  </si>
-  <si>
-    <t>Apa saja channel integrasi yang didukung Platform V3?</t>
-  </si>
-  <si>
-    <t>Channel integrasi meliputi Omnibotika, Webchat, Telegram, WhatsApp Business Solution (WABIS), Google Play, Line, Viber, atau API/Webhook.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara melihat tampilan chatbot yang sudah dibuat di Platform V3?</t>
-  </si>
-  <si>
-    <t>Ke menu persona, lalu klik “Test Here” yang ada di pojok kanan bawah layar untuk mencoba chatbot secara langsung.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara integrasi Webhook/API di Platform V3?</t>
-  </si>
-  <si>
-    <t>Webhook memungkinkan Botika mengirimkan event tertentu (misalnya pesan masuk, percakapan baru, atau status user) ke sistem eksternal menggunakan HTTP POST. Dengan begitu, setiap aktivitas chat bisa otomatis dicatat atau ditindaklanjuti di CRM, ERP, database internal, atau aplikasi bisnis lain.
-Kapan digunakan?
-- Ingin simpan data chat ke CRM/ERP.
-- Perlu trigger otomatis, misalnya setiap ada order baru lewat chat → otomatis masuk ke sistem internal.
-Manfaat utama:
-- Data percakapan sinkron dengan sistem internal.
-- Bisa buat automation lanjutan tanpa perlu manual input.
-📌 Ikuti link berikut untuk menemukan panduan integrasinya: 
-https://omni.botika.online/help-center/integrations/webhook.html</t>
-  </si>
-  <si>
-    <t>Apakah Demo bisa diulang setelah selesai?</t>
-  </si>
-  <si>
-    <t>Tidak bisa. Setelah selesai, pengguna bisa membuat perubahan langsung di dashboard.</t>
   </si>
   <si>
     <t>Integrasi Chatbot dengan Berbagai Channel</t>
@@ -284,669 +125,6 @@
   </si>
   <si>
     <t>KB Platform V3</t>
-  </si>
-  <si>
-    <t>Apa itu Platform V2?</t>
-  </si>
-  <si>
-    <t>Platform V2 adalah tempat untuk membuat dan mengelola aturan kerja chatbot, yaitu logika yang menentukan bagaimana bot merespons dan berinteraksi dengan pengguna. Anda bisa menyusun alur percakapan dengan mudah lewat tampilan drag &amp; drop, atau menulis custom code jika ingin pengaturan yang lebih spesifik.
-Selain itu, Platform V2 juga mendukung pembuatan chatbot berbasis NLP (Natural Language Processing), yang mampu memahami maksud dan konteks percakapan pengguna secara alami, seperti berbicara dengan manusia.</t>
-  </si>
-  <si>
-    <t>Apa saja kelebihan Platform V2?</t>
-  </si>
-  <si>
-    <t>Kelebihan Platform V2 antara lain yaitu :
-1) Menggunakan teknologi berbasis Natural Language Processing (NLP) untuk membuat aturan bot menjadi lebih pintar dalam memahami bahasa manusia. 
-2) Desain tampilannya yang mudah digunakan memungkinkan Anda merancang rule bot melalui tampilan visual (seperti drag &amp; drop) atau dengan menulis kode sendiri (Custom Code).
-3) Terintegrasi dengan produk Botika lainnya, jadi memudahkan manajemen dan koordinasi berbagai fungsi. 
-4) Anda juga bisa menduplikasi rule bot dan membuat logika bot dengan mudah, tanpa perlu kemampuan pemrograman yang dalam.</t>
-  </si>
-  <si>
-    <t>Apa saja Fitur Utama Platform V2?</t>
-  </si>
-  <si>
-    <t>Platform V2 memiliki 7 fitur utama, yaitu : 
-1) List Rule (Mengelola Rule) 
-2) Guide 
-3) Diagram (Chatbot designer untuk membuat alur bot) 
-4) Push Message 
-5) Intents 
-6) Entities 
-7) Knowledge Base.</t>
-  </si>
-  <si>
-    <t>Apa saja data yang dibutuhkan saat melakukan Registrasi akun Platform V2?</t>
-  </si>
-  <si>
-    <t>Saat mendaftar, data yang harus diisi adalah: Nama lengkap, Username, Phone Number, Email aktif (jangan pakai email palsu agar bisa menerima verifikasi berupa kode OTP), dan Password (buat password kuat, minimal 8 karakter dengan kombinasi huruf &amp; angka).</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Login ke Akun Platform V2?</t>
-  </si>
-  <si>
-    <t>Jika sudah punya akun, caranya login adalah : 
-1) Buka website Platform V2, kemudian klik tombol "Login".
-2) Masukkan email atau username &amp; password.
-3) Klik Next. Jika data benar, Anda akan masuk ke dashboard.</t>
-  </si>
-  <si>
-    <t>Akun Botika bisa dipakai login Platform V2?</t>
-  </si>
-  <si>
-    <t>Jika sebelumnya Anda sudah pernah membuat akun di produk Botika lain, akun itu bisa dipakai langsung untuk login ke Platform V2 tanpa harus daftar lagi. Cukup login dengan email &amp; password yang sama.</t>
-  </si>
-  <si>
-    <t>Bagaimana jika lupa Password akun Platform V2?</t>
-  </si>
-  <si>
-    <t>Jika Anda lupa password akun Platform V2, jangan khawatir. Di halaman login, klik opsi “Lupa password?”. Setelah itu, masukkan email yang terdaftar. Sistem akan mengirim instruksi reset password ke email Anda.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara reset Password akun Platform V2 dengan Email?</t>
-  </si>
-  <si>
-    <t>Cara reset Password akun Platform V2 dengan Email :
-1) Klik “Lupa password?”, masukkan email yang sudah terdaftar. 
-2) Buka email, salin kode OTP dan masukkan ke kolom verifikasi di halaman reset password. 
-3) Setelah verifikasi berhasil, buat password baru. 
-Tips: gunakan kombinasi huruf besar, huruf kecil, angka, dan simbol agar aman. 
-Contoh: Botika@2025.</t>
-  </si>
-  <si>
-    <t>Apa itu List Rule pada Platform V2?</t>
-  </si>
-  <si>
-    <t>List Rules pada Platform V2 menampilkan daftar semua rule yang ada. Dengan fitur ini, Anda bisa mengelola, mengedit, atau menambahkan rule baru dengan mudah.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara melakukan pencarian rule di Platform V2?</t>
-  </si>
-  <si>
-    <t>Anda dapat melakukan pencarian rule yang ada dengan cara berikut :
-1. Pada page Home https://platform.botika.online/app/home/ klik button search di kanan atas.
-https://drive.google.com/file/d/1mBG-5Cla3_tXA1eNire0jvrfSPFyPsVn/view?usp=drive_link
-2. Masukkan keyword yang ingin di cari, lalu klik button kanan untuk mulai search. Lalu pilih state yang muncul.
-https://drive.google.com/file/d/17Xc5lgxFD-cqrt0-E6R-n6cDILnIJ9ow/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Create Rule di Platform V2?</t>
-  </si>
-  <si>
-    <t>Anda dapat Create Rule baru pada Platform v2 dengan cara sebagai berikut : 
-1) Pada halaman list rules tekan tombol “ + ”. Masukkan nama, deskripsi serta pilih tipe (Private atau Public) untuk rule yang akan dibuat.
-2) Tekan tombol “Preview” dan pilih “Use Template” untuk konfirmasi penggunaan template.
-3) Selesai, maka Anda akan diarahkan ke halaman Diagram.
-Jika Anda ingin mempelajari lebih lanjut, silakan kunjungi tautan https://client.botika.online/docs/platform/#your-first-rule dan baca dokumentasi yang tersedia.</t>
-  </si>
-  <si>
-    <t>Apa itu Tipe Rule (Private)?</t>
-  </si>
-  <si>
-    <t>Tipe rule "Private" merupakan Rule yang hanya digunakan untuk diri sendiri saja.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Clone Rule di Platform V2?</t>
-  </si>
-  <si>
-    <t>Berikut merupakan cara clone rule pada platform v2. Anda dapat melakukan duplikasi/clone rule yang sudah ada baik ke akun sendiri maupun untuk akun lain dengan cara sebagai berikut :
-1) Pada page Home https://platform.botika.online/app/home/ tekan icon titik tiga pada rule yang ingin di clone.
-https://www.google.com/url?q=https://drive.google.com/file/d/13T8Bd-WZ5KZSevNc3UBScXWV8MTXjG4Y/view?usp%3Dsharing&amp;sa=D&amp;source=editors&amp;ust=1760581136667326&amp;usg=AOvVaw3yj1QGyV4LxigvPK6xXwC5
-2) Kemudian pilih “Clone”.
-https://drive.google.com/file/d/1z6iMT1gjglEJOuVtIYF7187_R-jQAknZ/view?usp=sharing
-3) Tentukan target clone. Pilih email jika ingin melakukan clone ke akun lain. Lengkapi data yang diperlukan dan klik tombol “Clone” untuk menyelesaikan proses.
-https://drive.google.com/file/d/15OGTluk7lFJ4VbK93Qs8ifEF_9Z3-SOx/view?usp=sharing</t>
-  </si>
-  <si>
-    <t>Apa maksud dari Target Clone Rule (My Account)?</t>
-  </si>
-  <si>
-    <t>Target clone "My Account" merupakan Target duplikat adalah ke akun itu sendiri.
-Contoh : Seseorang sudah punya Rule chatbot untuk FAQ Produk A, ia juga ingin membuat rule serupa untuk Produk B tanpa membuat dari awal. Maka ia clone Rule FAQ Produk A tersebut.</t>
-  </si>
-  <si>
-    <t>Apa maksud dari Target Clone Rule (Email)?</t>
-  </si>
-  <si>
-    <t>Target clone "Email" merupakan Target duplikat adalah ke email eksternal.
-Contoh : Seseorang telah membuat Rule untuk keperluan CS. Kebetulan temannya juga membutuhkan Rule serupa. Oleh karena itu Ia menduplikat Rule tersebut ke email temannya.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Edit Rule di Platform V2?</t>
-  </si>
-  <si>
-    <t>Anda dapat melakukan update / edit rule pada platform v2 dengan cara berikut : 
-1) Pada page Home https://platform.botika.online/app/home/ tekan titik tiga pada rule yang ingin Anda edit, Klik “Edit”. 
-2) Edit informasi rule sesuai dengan kebutuhan Anda. 
-3) Jika sudah sesuai maka tekan tombol “Update”.</t>
-  </si>
-  <si>
-    <t>Apa fungsi Fitur Guide di Platform V2?</t>
-  </si>
-  <si>
-    <t>Fitur Guide pada Platform v2 ini berfungsi sebagai panduan untuk membantu memahami cara menggunakan platform dengan benar dan maksimal. Sehingga dapat memudahkan Anda dalam perancangan rules bot.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Diagram pada Platform V2?</t>
-  </si>
-  <si>
-    <t>Diagram pada Platform v2 adalah tampilan chatbot designer yang dapat Anda gunakan untuk membuat alur untuk logika bot Anda. Fitur ini membantu Anda memvisualisasikan bagaimana bot akan merespon berbagai input dari pengguna.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Add State di Platform V2?</t>
-  </si>
-  <si>
-    <t>Anda bisa menambahkan state baru pada Platform v2 dengan langkah-langkah sebagai berikut :
-1) Masuk ke menu Diagram dan tekan “Add State”, lalu beri nama state baru dan klik "confirm".
-2) Atur Action dengan memilih Condition, menentukan Responds yang diinginkan, dan menambahkan Then.
-3) Simpan Action dengan memberi nama lalu tekan tombol "Save".</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Clone State di Platform V2?</t>
-  </si>
-  <si>
-    <t>Anda bisa melakukan duplikasi/clone State yang ada pada Platform v2 dengan langkah-langkah sebagai berikut : 
-1) Pada menu diagram, pilih state yang ingin diduplikasi, lalu klik ikon titik tiga dan pilih “Clone to New State”.
-2) Masukkan nama untuk state baru.
-3) Tekan “Confirm” untuk menyelesaikan.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Delete State di Platform V2?</t>
-  </si>
-  <si>
-    <t>Anda bisa menghapus State yang ada pada Platform v2 dengan langkah-langkah sebagai berikut : 
-1) Pada menu diagram, pilih state yang akan Anda hapus. 
-2) Kemudian klik titik tiga di atas dan tekan “Delete”. 
-3) Tekan tombol “Confirm”.</t>
-  </si>
-  <si>
-    <t>Apa itu Action?</t>
-  </si>
-  <si>
-    <t>Action merupakan bagian yang menentukan bagaimana bot akan berjalan dan berfungsi, semua logika bot dibangun di dalam action. Dalam action terdapat 3 bagian penting yaitu :
-1) Condition
-2) Responds
-3) Then
-Untuk penjelasan lebih detail mengenai Action bisa Anda lihat di https://client.botika.online/docs/platform/action.html.</t>
-  </si>
-  <si>
-    <t>Apa itu Condition?</t>
-  </si>
-  <si>
-    <t>Condition adalah suatu cara untuk menentukan apakah suatu action dapat dijalankan atau tidak. 
-Terdapat beberapa opsi Condition yaitu : 
-1) None Condition
-2) If Condition
-3) Simple Question &amp; Answer
-4) Goal Based
-5) Custom Code</t>
-  </si>
-  <si>
-    <t>Apa itu None Condition?</t>
-  </si>
-  <si>
-    <t>Sesuai dengan namanya yaitu None Condition maka tidak ada kondisi yang perlu dipenuhi. Jadi, action akan berjalan tanpa memeriksa kondisi apapun.
-Contoh : Bot selalu merespons “Oke” kepada pengguna, apa pun input yang diberikan.</t>
-  </si>
-  <si>
-    <t>Apa itu If Condition?</t>
-  </si>
-  <si>
-    <t>"If Condition" merupakan kondisi tertentu yang harus dipenuhi agar bot dapat menjalankan action. Jadi, action tersebut dapat berjalan jika kondisi telah dipenuhi terlebih dahulu.
-Contoh : Bot akan melanjutkan ke step Pendaftaran Member jika user memasukkan input lebih dari 18 (usia).
-Untuk lebih jelasnya Anda bisa melihat video dokumentasi pada link https://client.botika.online/docs/platform/example/video/condition.html.</t>
-  </si>
-  <si>
-    <t>Apa itu Condition Simple Question &amp; Answer?</t>
-  </si>
-  <si>
-    <t>"Simple Question &amp; Answer" merupakan kondisi berupa daftar pertanyaan, dimana bot melewati action ini jika memenuhi salah satu daftar pertanyaan yang ada, dan bot akan mengembalikan jawaban sesuai pertanyaan.
-Contoh : Terdapat daftar pertanyaan “Jam berapa toko buka?” dengan jawaban “Toko buka pukul 09.00 WIB.”
-Jika pengguna bertanya “Jam berapa toko buka?”, maka bot akan menjawab “Toko buka pukul 09.00 WIB.”
-Untuk lebih jelasnya Anda bisa melihat video dokumentasi pada link https://client.botika.online/docs/platform/example/video/condition.html</t>
-  </si>
-  <si>
-    <t>Apa itu Condition Goal Based?</t>
-  </si>
-  <si>
-    <t>"Goal Based" merupakan kondisi seperti formulir dimana pertanyaan diajukan secara berurutan hingga data terpenuhi.
-Contoh : Formulir pengisian email, user harus input email secara benar dimana harus mengandung "@". Jika tidak maka tidak akan lanjut ke step berikutnya.
-Untuk lebih jelasnya Anda bisa melihat video dokumentasi pada link https://client.botika.online/docs/platform/example/video/condition.html</t>
-  </si>
-  <si>
-    <t>Apa itu Condition Custom Code?</t>
-  </si>
-  <si>
-    <t>"Custom Code" merupakan kondisi yang mengharuskan logika pemrosesan rumit dan dibuat dengan bahasa PHP versi 5.
-Untuk lebih jelasnya Anda bisa melihat video dokumentasi pada link https://client.botika.online/docs/platform/example/video/condition.html#custom-code</t>
-  </si>
-  <si>
-    <t>Apa itu Responds?</t>
-  </si>
-  <si>
-    <t>Responds adalah bagian yang menentukan bagaimana hasil dari interaksi bot dengan pengguna setelah kondisi tertentu terpenuhi.
-Terdapat banyak opsi Responds yaitu :
-1) Text
-Fungsi ini digunakan untuk mengirimkan pesan berbentuk teks kepada pengguna.
-2) Random Text
-Fungsi random text adalah sebuah program atau perintah dalam komputer yang bertujuan untuk mengirimkan atau menampilkan teks secara acak dari sekumpulan teks yang sudah disiapkan sebelumnya.
-3) Text &amp; Button
-Fungsi text and button adalah sebuah fitur yang memungkinkan sistem mengirim teks bersamaan dengan tombol kepada pengguna.
-4) Button
-Fungsi button adalah sebagai tombol yang bisa ditekan oleh pengguna untuk melakukan suatu aksi, misalnya mengirim data, membuka halaman baru, atau memulai suatu proses di website atau aplikasi.
-5) Carousel
-Fungsi carousel adalah menampilkan beberapa konten dalam bentuk slide yang bisa digeser, masing-masing memiliki gambar, judul, deskripsi, dan tombol.
-6) Carousel &amp; Button
-Fungsi carousel dan button adalah untuk menampilkan beberapa konten bergambar secara bergantian (seperti slide) dengan informasi tambahan, seperti judul, deskripsi singkat, dan tombol aksi.
-7) Custom
-Fungsi custom menampilkan respon yang dapat disesuaikan dengan jenis message tertentu dan kapabilitas yang dimilikinya.
-8) Image
-Fungsi image adalah untuk mengirimkan gambar kepada pengguna melalui URL.
-9) Video
-Fungsi video adalah untuk mengirimkan video kepada pengguna melalui URL.
-10) Audio
-Fungsi audio adalah untuk menampilkan respon berupa audio yang diakses melalui URL.
-11) Document
-Fungsi document adalah untuk menampilkan respon berupa dokumen yang diakses melalui URL.
-12) Text to speech
-Fungsi text to speech adalah untuk menampilkan respon berupa teks disertai dengan audio hasil text-to-speech.
-13) Random text to speech
-Fungsi random text to speech adalah untuk menampilkan respon berupa teks disertai dengan audio hasil text-to-speech yang dipilih secara acak dari opsi yang ada. 
-14) JSON API
-Fungsi JSON API adalah untuk integrasi dengan server menggunakan metode GET atau POST.
-15) Transfer to human
-Fungsi Transfer to human adalah untuk mengoper percakapan ke helpdesk (Omnibotika) untuk ditangani. 
-16) Send email
-Fungsi send email adalah untuk mengirim email otomatis ke alamat email yang sudah ditentukan. 
-17) Send Transcript
-Fungsi send transcript adalah untuk mengirimkan salinan percakapan ke email yang sudah ditentukan.
-18) Set user variable
-Fungsi set user variable adalah untuk mengatur/menyimpan nilai variabel.
-19) Set Transaction
-Fungsi set transaction adalah untuk menyimpan atau mengelola status transaksi dalam sistem.
-20) Set user profile
-Fungsi set user profile adalah untuk menyimpan data profil user seperti nama, alamat, no telepon, jenis kelamin, foto profil dan tanggal lahir.
-21) Set user NPS
-Fungsi set user NPS adalah untuk mengatur skor NPS dimana digunakan untuk mengukur kepuasan pelanggan.
-22) Set input
-Fungsi set input adalah digunakan khusus pada phone channel untuk menentukan jenis input (voice, DTMF, interrupt) dan lama waktu tunggu sebelum timeout.
-23) Set Language
-Fungsi set language adalah untuk mengatur bahasa yang akan digunakan chatbot dalam berinteraksi dengan pengguna.
-24) Write report
-Fungsi write report adalah untuk membuat laporan (report) yang bisa dilihat di tampilan analytic di botmaster.
-25) Track analytic
-Fungsi track analytic adalah untuk melacak dan menganalisis frekuensi kunjungan pengguna pada menu-menu yang tersedia.
-26) Log
-Fungsi log adalah untuk mencatat informasi log.
-27) Comment
-Fungsi comment adalah untuk memberikan penjelasan tambahan dan tidak akan muncul di sisi user.
-Untuk lebih lengkapnya silakan cek link berikut: https://client.botika.online/docs/platform/action.html</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Text?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Text" ini menampilkan respon berupa teks. Anda bisa menambahkan responds text dengan cara : 
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Text”.
-2) Masukkan text respond.
-3) Klik save di pojok kanan atas.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Random Text?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Random Text" ini menampilkan respon berupa teks yang dipilih secara acak dari beberapa opsi yang ada. Anda bisa menambahkan responds random text dengan cara :
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi "Random Text".
-2) Masukkan beberapa text respond. Klik tombol “+” untuk menambah teks atau klik "ikon tempat sampah" untuk menghapus.
-3) Klik save di pojok kanan atas.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Text &amp; Button?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Text &amp; Button" ini menampilkan respon berupa teks disertai dengan tombol. Anda bisa menambahkan responds text &amp; button dengan cara berikut : 
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Text &amp; Button”.
-2) Masukkan text responds. Kemudian tekan tombol “+ BUTTON” untuk menambahkan button. Pada bagian “Button Title” isi nama tombol, lalu pada “Select Button Type”, pilih jenis tombol yang diinginkan. Berikut merupakan button type yang tersedia :
-- Button (Send Postback): mengirimkan pesan postback sebagai pesan dari pengguna.
-- Button (Open URL): membuka tautan di tab baru.
-- Button (Open Window Popup): membuka URL di jendela pop-up baru.
-- Button (Open Window Modal): menampilkan konten URL dalam overlay di bawah pesan.
-- Button (Share Location): meminta pengguna membagikan lokasi langsung.
-- Button (Phone Call): melakukan panggilan ke nomor yang dituju (khusus channel call; di webchat akan mengirim postback).
-3) Klik save di pojok kanan atas.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Button (Send Postback)?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Button (Send Postback)” akan mengirimkan text sebagai pesan postback dari pengguna ketika tombol diklik, Postback yaitu value atau payload yang dikirim ke sistem untuk disesuaikan dengan keyword yang sudah dipasang. Anda dapat menambahkan response button (send postback) dengan cara berikut :
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Button”, lalu tekan tombol yang ingin diedit.
-2) Isi judul tombol, pilih tipe “Send Postback”, dan masukkan nilai postback.
-3) Tekan “Save settings” untuk menyimpan. Gunakan “+ BUTTON” jika ingin menambah tombol lain.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Button (Open URL)?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Button (Open URL)” akan otomatis menuju URL yang dituju di tab baru. Anda bisa menambahkan responds button (Open URL) dengan cara sebagai berikut : 
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Button”, lalu tekan tombol yang ingin diedit.
-2) Isi judul tombol, pilih tipe “Open URL”, dan masukkan alamat URL.
-3) Tekan “Save settings” untuk menyimpan. Gunakan “+ BUTTON” jika ingin menambah tombol lain.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Button (Open window popup)?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Button (Open Window Popup)” akan otomatis menuju URL yang dituju di jendela baru. Anda bisa menambahkan responds button (Open window popup) dengan cara sebagai berikut : 
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Button”, lalu tekan tombol yang ingin diedit.
-2) Isi judul tombol, pilih tipe “Open Window Popup”, dan masukkan alamat URL.
-3) Tekan “Save settings” untuk menyimpan. Gunakan “+ BUTTON” bila ingin menambah tombol lain.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Button (Open window modal)?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Button (Open Window Modal)” akan ke konten dari URL yang dituju, dan akan dimuat di bawah dengan overlay. Anda bisa menambahkan responds button (Open window modal) dengan cara sebagai berikut : 
-1) Pilih jenis responds “Button”, lalu tekan tombol yang ingin diedit.
-2) Isi judul tombol, pilih tipe “Open Window Modal”, dan masukkan alamat URL.
-3) Tekan “Save settings” untuk menyimpan. Gunakan “+ BUTTON” bila ingin menambah tombol lain.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Button (Share location)?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Button (Share Location)” akan otomatis meminta user untuk membagikan lokasi user secara langsung. Anda bisa menambahkan responds button (Share location) dengan cara sebagai berikut :
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Button”, lalu tekan tombol yang ingin diedit.
-2) Isi judul tombol dan pilih tipe “Share Location”.
-3) Tekan “Save settings” untuk menyimpan. Gunakan “+ BUTTON” bila ingin menambah tombol lain.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Button (Phone Call)?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Button (Phone Call)” akan melakukan panggilan telepon ke nomor yang dituju. Namun, tipe ini digunakan untuk channel integrasi call saja, jika di webchat maka akan send postback. Anda bisa menambahkan responds button (Phone Call) dengan cara sebagai berikut : 
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Button”, lalu tekan tombol yang ingin diedit.
-2) Isi judul tombol, pilih tipe “Phone Call”, dan masukkan nomor telepon.
-3) Tekan “Save settings” untuk menyimpan. Gunakan “+ BUTTON” bila ingin menambah tombol lain</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Carousel?</t>
-  </si>
-  <si>
-    <t>Responds Carousel menampilkan respon dalam bentuk carousel yang berisi komponen gambar, judul, subjudul, dan tombol. Perlu diketahui bahwa Responds Carousel hanya dapat digunakan pada channel tertentu, seperti Facebook, LiveChat, LINE, dan Telegram. Namun untuk channel Telegram, carousel ditampilkan dalam bentuk vertikal.
-Langkah-langkah menambahkan Responds Carousel:
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi "Carousel".
-2) Lengkapi seluruh bagian carousel, mulai dari gambar, judul, subjudul, dan tombol.
-3) Tekan tombol “+ BUTTON” untuk menambah tombol, ikon tempat sampah untuk menghapus card, atau “+ Add card” untuk menambah card baru.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Carousel &amp; Button?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Carousel &amp; Button" menampilkan responds berupa gabungan antara carousel dan tombol tambahan di luar carousel. Perlu diperhatikan bahwa Responds Carousel hanya dapat digunakan pada channel tertentu, seperti Facebook, LiveChat, dan LINE.
-Anda dapat menambahkan Responds Carousel &amp; Button dengan langkah-langkah berikut:
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Carousel &amp; Button”.
-2) Lengkapi bagian carousel (gambar, judul, subjudul, tombol dalam, dan tombol luar).
-3) Gunakan tombol “+ BUTTON” untuk menambahkan tombol, ikon tempat sampah untuk menghapus card, atau “+ Add card” untuk menambahkan card baru.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Image?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Image" menampilkan responds berupa gambar yang diakses melalui URL. Anda dapat menambahkan responds Image dengan langkah-langkah berikut:
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Image”.
-2) Tekan “Add Image” dan masukkan URL gambar yang ingin ditambahkan.
-3) Kemudian tekan “Done”.
-Jika Anda tidak memiliki gambar yang dapat diakses melalui URL, Anda dapat terlebih dahulu menyimpan gambar tersebut melalui Botmaster → Resource, kemudian gunakan URL dari resource tersebut untuk ditambahkan pada responds Image.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Video?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Video" menampilkan responds berupa video yang diakses melalui URL. Anda dapat menambahkan responds Video dengan cara berikut:
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Video”.
-2) Masukkan URL dari video yang ingin ditampilkan.
-3) Jika Anda tidak memiliki video yang diakses melalui URL, Anda dapat menyimpannya terlebih dahulu melalui Botmaster → Resources, lalu gunakan tautan dari video tersebut.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Text to speech?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Text to Speech" menampilkan responds berupa teks yang disertai dengan audio hasil text-to-speech. Anda dapat menambahkan responds Text to Speech dengan cara berikut:
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “Text to Speech”, lalu masukkan teks yang ingin diubah menjadi suara.
-2) Pilih tipe/karakter suara serta bahasa yang diinginkan. Sebelum disimpan, hasil dapat diuji dengan menekan ikon speaker di sebelah kanan (setelah memilih bahasa yang diinginkan).
-3) Simpan untuk menyelesaikan.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds JSON API?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "JSON API" digunakan untuk mengintegrasikan dengan API menggunakan metode GET atau POST. Anda bisa menambahkan responds JSON API dengan cara berikut : 
-1) Buka action pada state, kemudian pada bagian "responds" pilih opsi “JSON API”, lalu tentukan metode GET atau POST dan masukkan URL.
-2) Tambahkan header (bila diperlukan) serta lengkapi informasi sesuai tipe yang dipilih.
-3) Uji permintaan dengan “Test the Request”, lalu centang save responds to user variable dan isi nama variabel untuk menyimpan hasil.
-Pada implementasinya metode GET dan POST memiliki beberapa perbedaan diantaranya : 
-Metode GET 
-- digunakan untuk mengambil data dari server
-- tidak memerlukan body request untuk mengambil datanya
-- cocok untuk permintaan yang hanya membaca data, seperti menampilkan daftar produk atau profil pengguna.
-POST
-- digunakan untuk mengirim data ke server
-- data dikirim melalui body request
-- cocok untuk menyimpan, memperbarui, atau memproses data, seperti mengirim formulir, membuat pesanan, atau menyimpan input pengguna."</t>
-  </si>
-  <si>
-    <t>Bagaimana cara set Responds JSON API (POST)?</t>
-  </si>
-  <si>
-    <t>Cara set Responds JSON API tipe POST maka Anda perlu : 
-1) Pilih opsi body “JSON” atau “URL Encoded”.
-2) Jika memilih “JSON”, masukkan kode sesuai sintaks JSON; jika memilih “URL Encoded”, masukkan judul dan nilai.
-3) Gunakan tombol “+ Parameter” untuk menambah parameter atau ikon tempat sampah untuk menghapus.</t>
-  </si>
-  <si>
-    <t>Apa itu Responds Transfer to human?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Transfer to human" untuk mengoper percakapan ke helpdesk (Omnibotika) untuk ditangani. Anda bisa menambahkan responds Transfer to human dengan cara berikut: 
-1) Buka action pada state, kemudian pada bagian "responds" pilih “Transfer to Human”, lalu tentukan tujuan: Any available agent, Specific Agent, atau Specific Department.
-2) Lengkapi data sesuai pilihan (misalnya alamat email/nama departemen, start message, error message if agent not available, subject, dan category bila diperlukan).
-3) (Opsional) Centang “Put user in queue and inform when agent is busy” untuk memasukkan pengguna ke antrian bila agen sedang sibuk, lalu simpan pengaturan.</t>
-  </si>
-  <si>
-    <t>Responds Set input digunakan untuk apa?</t>
-  </si>
-  <si>
-    <t>Opsi Responds "Set Input" digunakan khusus pada phone channel untuk menentukan jenis input (voice &amp; text, DTMF (Dual-Tone Multi-Frequency), interrupt) dan lama waktu tunggu sebelum timeout. Anda bisa menambahkan responds Set input dengan cara berikut : 
-1) Buka action pada state, kemudian pada bagian "responds" pilih “Set input”. 
-2) Pilih opsi input dan isi informasi yang diperlukan. 
-3) Save.</t>
-  </si>
-  <si>
-    <t>Responds Set input "DTMF" digunakan untuk apa?</t>
-  </si>
-  <si>
-    <t>Fitur ini digunakan untuk mengenali tekanan tombol pada telepon sebagai bentuk input. Setiap tombol yang ditekan menghasilkan nada tertentu yang dibaca oleh sistem sebagai perintah. Setelah selesai menggunakan DTMF, pengaturan sebaiknya dikembalikan ke mode Voice &amp; Text supaya sistem bisa berfungsi normal kembali dan mengenali input suara atau teks.
-Perlu diketahui najwa opsi ini hanya bisa digunakan pada channel phone saja.
-Anda bisa menambahkan responds Set input "DTMF (Dual-Tone Multi-Frequency)" dengan cara berikut :
-1) Pilih opsi input "DTMF"
-2) Masukkan nilai pada kolom Max, yaitu jumlah digit yang harus ditekan pengguna menggunakan keypad sebelum aturan dijalankan secara otomatis. Masukkan 0 untuk jumlah digit tidak terbatas (pengguna harus menekan # atau * untuk mengakhiri input secara manual).
-3) Save.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara duplikat Responds?</t>
-  </si>
-  <si>
-    <t>Anda dapat menduplikat responds ke state atau action yang lain dengan cara sebagai berikut : 
-1) Tekan titik tiga pada respon yang ingin di duplikat, Kemudian pilih opsi “Copy”. 
-2) Pilih state dan action tujuan untuk hasil duplikat respon. 
-3) Kemudian tekan tombol “Copy”.</t>
-  </si>
-  <si>
-    <t>bagaimana cara memindahkan Responds rule pada platform v2?</t>
-  </si>
-  <si>
-    <t>Anda dapat memindah responds rule ke state atau action yang lain dengan cara sebagai berikut : 
-1) Tekan ikon titik tiga pada responds yang ingin dipindahkan, lalu pilih opsi “Move”.
-2) Tentukan state dan action tujuan pemindahan.
-3) Tekan tombol “Move” untuk menyelesaikan.</t>
-  </si>
-  <si>
-    <t>Test Here pada Diagram Platform V2 digunakan untuk apa?</t>
-  </si>
-  <si>
-    <t>“Test Here” pada Platform V2 digunakan untuk menguji flow/alur bot yang telah Anda buat. Dengan fitur ini, Anda bisa memeriksa bagaimana bot ketika berinteraksi dengan pengguna. Anda bisa menggunakan fitur ini dengan cara berikut : 
-1) Masuk ke menu Diagram. 
-2) Kemudian tekan tombol “Test Here” di bagian bawah menu Diagram. 
-3) Ketik dan kirim pesan uji coba.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Create Push Message?</t>
-  </si>
-  <si>
-    <t>Anda dapat Create Push Message dengan cara sebagai berikut : 
-1) Masuk ke menu Push Message lalu tekan tombol "+ Create Push Message". 
-2) Lengkapi informasi seperti Pushmessage Name, Description, Push Time (minutes), dan State to run (state tujuan yang akan di tampillkan). 
-3) Tekan tombol "Create Push Message".</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Import Intent?</t>
-  </si>
-  <si>
-    <t>Anda dapat menggunakan fitur Import Intent dengan cara sebagai berikut :
-1) Buka menu Intents pada bagian My Intents, lalu klik tombol “+ Import Intent”.
-2) Unduh dan isi file contoh sample.csv (opsional), kemudian unggah kembali dengan menekan tombol “Choose File”.
-3) Setelah data intent muncul, pastikan isinya sudah benar, lalu klik “Import Intent” untuk menyelesaikan proses.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Import Entity?</t>
-  </si>
-  <si>
-    <t>Anda dapat menggunakan fitur Import Entities dengan cara sebagai berikut :
-1) Buka menu Entities pada bagian My Entities, lalu klik tombol “+ Import entity”.
-2) Unduh dan isi file contoh sample.csv (opsional), kemudian unggah kembali dengan menekan tombol “Choose File”.
-3) Setelah data entity muncul, pastikan isinya sudah benar, lalu klik “Import entity” untuk menyelesaikan proses.</t>
-  </si>
-  <si>
-    <t>Apa itu Manage Article pada menu Knowledge Base Platform V2?</t>
-  </si>
-  <si>
-    <t>Manage Article pada knowledge base Platform V2 adalah fitur untuk mengelola artikel-artikel yang sudah ada di Knowledge Base. Di menu Manage Artikel, Anda bisa melakukan hal-hal berikut :
-1) Edit Category
-2) Edit Sub Category
-3) Edit Article
-4) Delete Article</t>
-  </si>
-  <si>
-    <t>Bagaimana cara edit Sub Category pada Knowledge Base Platform V2?</t>
-  </si>
-  <si>
-    <t>Anda bisa mengedit sub category pada knowledge base Platform V2 dengan cara sebagai berikut : 
-1) Masuk ke Artikel Manager, kemudian tekan tombol dropdown pada kategori utama. 
-2) Tekan tombol pen pada bagian sub category. 
-3) Edit nama sub-category atau ubah kategori utamanya, lalu tekan tombol “Save”.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara edit artikel pada Knowledge Base Platform V2?</t>
-  </si>
-  <si>
-    <t>Anda bisa edit artikel pada knowledge base Platform V2 dengan cara sebagai berikut : 
-1) Masuk ke Artikel Manager, kemudian tekan tombol pen pada bagian Artikel yang ingin di edit.
-2) Edit artikel sesuai keinginan Anda.
-3) Jika sudah selesai maka tekan tombol “Save”.</t>
-  </si>
-  <si>
-    <t>Menu Pilih Bahasa pada Platform V2 digunakan untuk apa?</t>
-  </si>
-  <si>
-    <t>Menu Pilih Bahasa pada Platform V2 digunakan untuk memilih bahasa yang akan digunakan pada Platform V2. Terdapat dua opsi bahasa, yaitu Bahasa Indonesia (id-ID) Bahasa Inggris (en-US)</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Logout dari Platform V2?</t>
-  </si>
-  <si>
-    <t>Untuk keluar dari Platform V2, klik ikon profil di kanan atas, lalu pilih Logout. Anda akan diarahkan ke halaman utama, dan sesi login akan berakhir.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara membuat formatting/styling response text di platform v2?</t>
-  </si>
-  <si>
-    <t>Untuk menerapkan formatting atau styling pada response text di platform V2, kamu bisa mengikuti panduan resminya. Klik link berikut https://client.botika.online/docs/platform/limitation-channels.html</t>
-  </si>
-  <si>
-    <t>Di rule nya platform v2 gimana cara dapetin tipe messenger di platform?</t>
-  </si>
-  <si>
-    <t>Untuk mendapatkan tipe messenger di Platform V2, Anda bisa melakukannya melalui pengaturan Rule. Berikut langkah-langkahnya:
-1. Buka menu "Rules" di Platform V2, lalu klik rule yang ingin Anda edit atau buat rule baru.
-2. Pada pengaturan rule, tambahkan kondisi atau aksi yang menggunakan tipe messenger sebagai salah satu parameter, misalnya dengan {{user.messengerType}} untuk menentukan tipe messenger dalam flow.
-3. Simpan perubahan dan sesuaikan alur percakapan sesuai tipe messenger yang digunakan pengguna.
-Dokumentasi lebih lengkap bisa dilihat di link berikut:
-https://client.botika.online/docs/platform/variable.html#get-user-messenger-type 
-Dengan cara ini, Anda dapat mengatur alur percakapan yang berbeda berdasarkan tipe messenger yang digunakan pengguna. Jika ada yang kurang jelas atau butuh penjelasan lebih lanjut, jangan ragu untuk bertanya!</t>
-  </si>
-  <si>
-    <t>KB PLATFORM V2</t>
-  </si>
-  <si>
-    <t>Apa itu Online Agent di Home Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Online Agent di Omnibotika V2 menunjukkan jumlah agen yang sedang aktif atau login di dashboard Omnibotika V2. Data ini membantu supervisor mengetahui siapa saja yang tersedia untuk menerima dan menangani tiket dari pelanggan.</t>
-  </si>
-  <si>
-    <t>Apa itu Average Agent Response Time di Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Average Agent Response Time di Omnibotika V2 adalah rata-rata waktu yang dibutuhkan seorang agen untuk merespon tiket setelah tiket tersebut ditugaskan kepadanya. Indikator ini lebih fokus mengukur performa per agen.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara menambahkan file ke chat di Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Di Omnibotika V2, Anda bisa mengirim file langsung ke pelanggan melalui Chat Console. Fitur ini memudahkan saat perlu berbagi dokumen, gambar, atau lampiran lain. Berikut langkahnya:
-1) Buka percakapan di menu Chat Console Omnibotika V2.
-2) Klik ikon + lalu pilih file dari komputer atau langsung drag &amp; drop file yang dibutuhkan.
-3) Tekan Send untuk mengirim file ke pelanggan.</t>
-  </si>
-  <si>
-    <t>Apa itu Customer Journey di menu chat Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Customer Journey di Omnibotika V2 menampilkan riwayat interaksi pelanggan sejak pertama kali berinteraksi dengan bisnis. Agen bisa melihat percakapan sebelumnya, tiket yang pernah dibuat, hingga respon yang diberikan, sehingga agen lebih memahami konteks kebutuhan pelanggan. Selain itu, journey juga terintegrasi dengan merge contact, sehingga dapat melihat aktivitas user meski berbeda channel.</t>
-  </si>
-  <si>
-    <t>Apa itu Chat Summary di menu chat Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Chat Summary di Omnibotika V2 adalah ringkasan otomatis dari percakapan antara pelanggan dan agen di Omnibotika V2. Fitur ini membantu menampilkan inti topik dan solusi yang diberikan sehingga supervisor bisa memahami hasil interaksi tanpa perlu membaca seluruh isi chat.</t>
-  </si>
-  <si>
-    <t>Apa itu laporan Customer Satisfaction di menu Report Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Laporan Customer Satisfaction (CSAT) di Omnibotika V2 menunjukkan hasil survei kepuasan pelanggan yang dikirim setelah tiket selesai. Data ini memberi gambaran kualitas layanan berdasarkan feedback pelanggan.</t>
-  </si>
-  <si>
-    <t>Apa itu Average Agent Response Time di menu Report Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Average Agent Response Time di menu report Omnibotika V2 menunjukkan rata-rata waktu respon dari masing-masing agen setelah tiket dialokasikan ke mereka. Berguna untuk mengukur performa individu.</t>
-  </si>
-  <si>
-    <t>Apa perbedaan Omnibotika V2 dan Omnibotika V1 di Botika?</t>
-  </si>
-  <si>
-    <t>Omnibotika V2 hadir dengan fitur-fitur baru yang lebih canggih dibandingkan versi sebelumnya. Di versi ini, Anda bisa melayani pelanggan dengan lebih mudah, permintaan layanan yang lebih terstruktur, dan sistem manajemen percakapan yang lebih pintar.
-Selain itu, tampilan antarmuka Omnibotika V2 lebih mudah digunakan dan lebih ramah pengguna, sehingga proses pengelolaan tiket dan komunikasi pelanggan jadi lebih cepat dan efisien.</t>
-  </si>
-  <si>
-    <t>Bagaimana jika akun admin Omni tidak bisa login karena session masih aktif?</t>
-  </si>
-  <si>
-    <t>Jika akun admin Anda tidak bisa login karena session masih aktif, Anda bisa melakukan logout dari session yang sedang aktif terlebih dahulu.
-Biasanya hal ini terjadi karena akun masih terhubung di perangkat lain atau belum keluar dengan benar dari sesi sebelumnya.
-Setelah logout, coba login kembali seperti biasa. Jika masalah tetap muncul, Anda bisa hubungi support@botika.online untuk membantu reset session akun Anda.</t>
   </si>
   <si>
     <t>Bagaimana cara registrasi akun Omnibotika V2?</t>
@@ -963,789 +141,138 @@
 Selamat mencoba, dan semoga bisnis Anda semakin sukses!</t>
   </si>
   <si>
-    <t>Dokumentasi Platform</t>
-  </si>
-  <si>
     <t>Untuk membuat bot dengan Omnibotika, biasanya prosesnya cukup fleksibel. Kamu bisa mendapatkan panduan lengkap untuk membuat dan menyesuaikan chatbot sesuai kebutuhan bisnismu. Omnibotika menyediakan opsi untuk membuat bot dari awal atau menyesuaikan bot yang sudah ada agar sesuai dengan kebutuhan spesifikmu.
 Jika kamu memerlukan panduan langkah atau bantuan lebih lanjut dalam proses pembuatan dan penyesuaian bot, Anda bisa melihat dokumentasi pada link https://docs.google.com/document/d/1O-ci1sM10-HirrK7gN3xHltUzfk_MoRbnDewwqkfTBk/edit?usp=drive_link. 
 Semoga sukses dengan pembuatan chatbot-mu!</t>
   </si>
   <si>
-    <t>KB Omnibotika V2</t>
+    <t>Apakah ada paket Chatbot Gen AI?</t>
   </si>
   <si>
-    <t>Apa saja kelebihan Omnibotika V1?</t>
+    <t>Tentu! Chatbot Gen AI Profesional dirancang khusus untuk perusahaan besar yang menangani volume pelanggan tinggi dan membutuhkan sistem layanan otomatis yang cepat serta responsif.
+Paket ini mendukung hingga 10.000 MAU (Monthly Active Users) dengan harga Rp15.000.000 per bulan, dan sudah termasuk bonus 5 lisensi Omnichannel by Botika untuk membantu tim Anda mengelola komunikasi pelanggan di berbagai channel dengan lebih efisien.
+Cocok untuk organisasi besar yang ingin meningkatkan kualitas interaksi pelanggan sambil menjaga produktivitas dan kecepatan layanan.</t>
   </si>
   <si>
-    <t>Kelebihan Omnibotika v1 antara lain yaitu :
-1) Integrasi yang mudah
-OmniBotika v1 mudah untuk diintegrasiin dengan berbagai channel komunikasi seperti WhatsApp, E-mail, Telepon, dan aplikasi instant messenger lainnya. Jadi, Anda bisa mengelola semua komunikasi dari satu tempat.
-2) Integrasi dengan Chatbot
-OmniBotika v1 dapat diintegrasi dengan chatbot, sehingga dapat membantu membalas pesan yang masuk ketika agent sedang tidak available atau offline. Jadi, komunikasi tetap lancar tanpa hambatan.
-3) Konektivitas Multi-Channel
-Anda bisa langsung terhubung dengan berbagai platform komunikasi, memudahkan buat berinteraksi dengan pelanggan melalui banyak saluran sekaligus.</t>
+    <t>KB Pricelist Dan SLA Botika</t>
   </si>
   <si>
-    <t>Bagaimana cara registrasi akun ke Omnibotika V1?</t>
+    <t>Apa itu WhatsApp Business Call?</t>
   </si>
   <si>
-    <t>Sebelum dapat menggunakan OmniBotika, Anda perlu membuat akun terlebih dahulu. Prosesnya mudah, ikuti tiga langkah berikut:
-1) Buka situs https://omni.botika.online/register lalu klik “Sign Up” jika Anda belum memiliki akun.
-2) Isi data diri Anda, seperti email aktif, kata sandi, nama lengkap, username, dan nomor telepon. Jika memiliki kode promo, Anda dapat memasukkannya. Setelah itu, klik “Create Account”.
-3) Periksa email Anda, lalu klik “Confirm Email Address” untuk mengaktifkan akun.
-Setelah konfirmasi selesai, akun Anda siap digunakan.</t>
+    <t>WhatsApp Business Call adalah fitur resmi dari Meta yang memungkinkan bisnis melakukan dan menerima panggilan suara langsung melalui akun WhatsApp Business API. Dengan layanan ini, perusahaan bisa berinteraksi dengan pelanggan lewat suara secara lebih cepat, efisien, dan profesional tanpa harus menggunakan pulsa telepon biasa. Di Botika, fitur ini juga bisa diintegrasikan dengan Voicebot AI, IVR, dan sistem call center agar proses komunikasi menjadi otomatis namun tetap terasa natural.</t>
   </si>
   <si>
-    <t>Bagaimana jika lupa kata sandi akun di Omnibotika V1?</t>
+    <t>Apakah WhatsApp Business Call aman digunakan?</t>
   </si>
   <si>
-    <t>Jika Anda lupa kata sandi akun di Omnibotika V1, lakukan langkah berikut: 
-1) Di halaman login, klik “Forget Password?” lalu masukkan email Anda.
-2) Buka email, tekan tombol "Reset Password" atau link yang dilampirkan untuk diarahkan ke halaman reset password.
-3) Di halaman reset password, buat kata sandi baru, lalu klik "Reset Password" untuk menyimpan password baru.</t>
+    <t>Sangat aman. Semua komunikasi melalui Botika dienkripsi end-to-end sesuai kebijakan Meta. Selain itu, setiap panggilan dicatat secara aman dan hanya bisa diakses oleh petugas berwenang. Server Botika juga dilindungi dengan sistem keamanan berlapis agar data pelanggan tetap terlindungi.</t>
   </si>
   <si>
-    <t>Apa itu role Agent pada Omnibotika V1?</t>
+    <t>Apakah layanan ini bisa diintegrasikan dengan CRM perusahaan?</t>
   </si>
   <si>
-    <t>Role Agent pada Omnibotika V1 mendapat akses ke menu home, ticket dan chat console.
-Tugas agent yaitu menghandle chat, e-mail dan call dari customer.</t>
+    <t>Bisa. Botika menyediakan integrasi API dan webhook untuk menghubungkan data panggilan dengan CRM, sistem tiket, atau platform customer service lainnya. Jadi, semua interaksi pelanggan—baik yang lewat chat maupun panggilan—bisa terekam otomatis dalam satu sistem.</t>
   </si>
   <si>
-    <t>Apa fungsi opsi Follow Up pada Chat Console Omnibotika V1?</t>
+    <t>Bagaimana kalau pelanggan sedang dalam panggilan lain?</t>
   </si>
   <si>
-    <t>Follow Up pada Chat Console OmniBotika v1 memiliki peran yang sangat penting untuk menjaga komunikasi dengan pelanggan. Kadang, ada pelanggan yang meninggalkan percakapan sebelum selesai. Melalui fitur ini, kamu tetap bisa menghubungi mereka kembali lewat email. Dengan begitu, informasi penting tidak terlewat, komunikasi tetap terjaga, dan pelanggan merasa diperhatikan. Fitur ini juga membantu meningkatkan kepuasan pelanggan karena setiap kebutuhan mereka tetap ditindaklanjuti dengan baik.</t>
+    <t>Jika pelanggan sedang melakukan panggilan lain, sistem akan menandai panggilan sebagai “busy” dan menjadwalkan ulang secara otomatis beberapa menit kemudian. Hal ini memastikan tidak ada gangguan dan panggilan bisa tetap dilakukan di waktu terbaik.</t>
   </si>
   <si>
-    <t>Bagaimana cara kerja Omnibotika V1?</t>
+    <t>Kalau WhatsApp saya diblokir, apakah layanan tetap bisa digunakan?</t>
   </si>
   <si>
-    <t>OmniBotika V1 adalah platform pusat komunikasi bisnis yang mengelola interaksi pelanggan dari berbagai channel dalam satu tempat.
-Cara kerjanya:
-1) Daftar di omni.botika.online dan masuk ke dashboard untuk mulai mengatur integrasi. 
-2) Hubungkan channel seperti WhatsApp, Facebook Messenger, dan LINE. 
-3) Gunakan fitur OmniBotika V1 seperti chatbot multichannel dan analisis performa agen. Jika Anda membutuhkan bantuan bisa menghubungi support@botika.online.
-Dengan OmniBotika V1, komunikasi bisnis jadi lebih efisien, terpusat, dan profesional.</t>
+    <t>Tidak bisa. Jika nomor bisnis diblokir oleh Meta, seluruh aktivitas panggilan otomatis akan berhenti. Namun, hal ini jarang terjadi jika bisnis mematuhi kebijakan komunikasi WhatsApp Business API.</t>
   </si>
   <si>
-    <t>Apa itu fitur Contacts pada Omnibotika V1?</t>
+    <t>Nomor yang digunakan untuk nelpon itu nomor saya atau nomor perusahaan?</t>
   </si>
   <si>
-    <t>Fitur “Contacts” di OmniBotika v1 adalah tempat untuk menyimpan dan mengatur data pelanggan atau klien dengan rapi, seperti buku telepon digital. Melalui fitur ini, kamu bisa menambah, mengubah, atau menggabungkan data kontak sesuai kebutuhan. Namun, perlu diketahui bahwa meskipun data sudah tersimpan di Contact Book, sistem ini belum bisa digunakan untuk langsung mengirim pesan atau memulai chat dengan kontak tersebut. Jika membutuhkan informasi lebih lanjut atau ingin bertanya, kamu dapat menghubungi Botika melalui email di support@botika.online. Dengan fitur ini, seluruh data kontak akan tetap tersusun dengan baik, akurat, dan mudah diakses, sehingga komunikasi dengan pelanggan dapat berjalan lebih efektif.</t>
+    <t>Nomor yang digunakan adalah nomor bisnis resmi perusahaan yang sudah diverifikasi. Jadi, pelanggan akan melihat panggilan berasal dari akun WhatsApp bisnis dengan identitas dan logo perusahaan Anda.</t>
   </si>
   <si>
-    <t>Apakah infomasi kontak pada Omnibotika V1 bisa diubah?</t>
+    <t>Kalau pelanggan membalas dengan chat setelah panggilan, apakah sistem bisa merespons?</t>
   </si>
   <si>
-    <t>Bisa, Anda dapat mengubah informasi kontak pada Omnibotika V1 dengan cara sebagai berikut : 
-1) Masuk ke menu "Contacts". Klik "icon titik tiga" di samping kontak dan pilih opsi "Edit"
-2) Anda bisa mengubah berbagai informasi mulai dari nama, email, no telepon, dan lain sebagainya.
-3) Tekan tombol "Save".</t>
+    <t>Bisa. Sistem kami mendukung mode hybrid, artinya pelanggan bisa melanjutkan komunikasi lewat chat setelah panggilan, dan sistem tetap bisa menjawab otomatis atau meneruskan ke agen manusia bila dibutuhkan.</t>
   </si>
   <si>
-    <t>Dimana kita bisa melihat laporan peforma agent di Omnibotika V1?</t>
+    <t>Apakah bisa menggunakan nomor luar negeri untuk WhatsApp Call?</t>
   </si>
   <si>
-    <t>Di OmniBotika V1, kamu bisa melihat laporan kinerja agen melalui menu "Reports", lalu pilih tab "Agent".
-Terdapat beberapa jenis laporan, yaitu:
-1) Summary Agent
-2) Agent Performance Chart
-3) Agent Performance Chart Interval
-Semua laporan bisa disesuaikan dengan periode waktu tertentu dan diunduh dalam format CSV, Excel, PDF, dan lainnya.</t>
+    <t>Bisa, asalkan nomor tersebut aktif, terdaftar di WhatsApp Business, dan wilayahnya didukung oleh kebijakan Meta. Sistem otomatis akan memverifikasi status nomor sebelum memulai panggilan.</t>
   </si>
   <si>
-    <t>Apa itu All Tickets pada fitur Report di fitur Ticket?</t>
+    <t>Bagaimana cara menghentikan layanan WhatsApp Call jika tidak ingin lanjut berlangganan?</t>
   </si>
   <si>
-    <t>All Tickets adalah fitur untuk menampilkan jumlah keseluruhan tiket, termasuk yang berstatus new, open, solved, dan hold dalam periode waktu yang dipilih.</t>
+    <t>Kamu bisa menghentikan layanan dengan menonaktifkan akun bisnis yang digunakan atau menghubungi tim support Botika untuk penghentian akses agar nomor tidak lagi melakukan panggilan otomatis.</t>
   </si>
   <si>
-    <t>Apa itu Handled Tickets by Agents pada fitur Report di fitur Ticket?</t>
+    <t>Apakah ada pelatihan untuk tim saya setelah aktivasi layanan?</t>
   </si>
   <si>
-    <t>Handled Tickets by Agents adalah fitur yang menampilkan jumlah tiket New yang sudah diproses atau dirouting ke agen.</t>
+    <t>Ada. Tim Botika menyediakan sesi onboarding dan training agar tim Anda paham cara menggunakan dashboard, laporan, serta fitur otomatisasi panggilan.</t>
   </si>
   <si>
-    <t>Apa itu Summary Reporting pada menu Report di fitur Ticket?</t>
+    <t>Apakah sistem bisa menggabungkan WhatsApp Call dengan chatbot teks?</t>
   </si>
   <si>
-    <t>Fitur Summary Reporting berfungsi untuk menampilkan ringkasan laporan yang memberikan gambaran umum tentang aktivitas tiket di sistem. Di OmniBotika, kamu dapat melihatnya pada menu Home. Di sana terdapat grafik yang menunjukkan jumlah tiket berdasarkan status (New, Open, Solved), informasi tentang SLA in dan SLA out, rata-rata waktu untuk merespons dan menyelesaikan tiket, serta tren jumlah tiket setiap hari.</t>
+    <t>Bisa banget. Layanan Botika mendukung integrasi hybrid antara voicebot dan chatbot teks. Jadi, pelanggan bisa mulai dengan panggilan suara, lalu melanjutkan obrolan lewat chat tanpa kehilangan konteks percakapan.</t>
   </si>
   <si>
-    <t>Apa itu Total Tickets per Channel pada menu Report di fitur Ticket?</t>
+    <t>KB WA Call</t>
   </si>
   <si>
-    <t>Fitur Total Tickets per Channel berfungsi untuk menampilkan jumlah tiket yang diterima dari setiap channel yang terhubung ke OmniBotika pada hari itu. Data ini bisa kamu lihat di menu Home, pada bagian “Today Ticket per Channel”. Informasi ini berguna untuk mengetahui dari channel mana saja tiket masuk dan berapa jumlahnya.</t>
+    <t>aku mau buat chatbot, berikan aku Dokumentasi Platform</t>
   </si>
   <si>
-    <t>Apa itu menu Agent pada fitur Report pada Omnibotika V1?</t>
+    <t>Apa saja platform yang bisa diintegrasikan dengan voicebot Botika?</t>
   </si>
   <si>
-    <t>Menu Agent Report pada OmniBotika V1 digunakan untuk menampilkan laporan aktivitas dan kinerja agen melalui beberapa tab utama, yaitu:
-1) Summary Agent – berisi ringkasan tiket, status, waktu penanganan, dan riwayat login setiap agen.
-2) Performance Chart – menampilkan grafik kinerja agen berdasarkan waktu dan channel.
-3) Performance Chart Interval – menampilkan laporan performa agen berdasarkan periode waktu tertentu.
-Semua laporan dapat difilter berdasarkan tanggal dan diunduh dalam format CSV, Excel, atau gambar, sehingga memudahkan proses evaluasi kinerja.</t>
+    <t>Apa saja metrics dan fitur analytics yang tersedia di dashboard voicebotika?</t>
   </si>
   <si>
-    <t>Apa itu Summary Agent pada menu Report di fitur Agent?</t>
+    <t>Apakah voicebot bisa menyimpan data pelanggan dan jadwal pembayaran untuk kebutuhan penagihan?</t>
   </si>
   <si>
-    <t>Fitur Summary Agent adalah untuk menampilkan ringkasan dari semua tiket yang telah ditangani oleh setiap agen. Informasi yang ditampilkan mencakup status tiket, rata-rata waktu penanganan, rata-rata waktu respon, waktu terakhir agen login, serta status aktif agen. Tampilan laporan dapat disesuaikan berdasarkan periode tanggal tertentu dan dapat diunduh dalam format CSV atau Excel.</t>
+    <t>Apakah voicebot Botika sudah menggunakan Generative AI dan bisa terhubung ke payment gateway?</t>
   </si>
   <si>
-    <t>Apa itu Performance Chart pada menu Report di fitur Agent?</t>
+    <t>Apakah voicebot Botika sudah memiliki fitur sentiment analytics?</t>
   </si>
   <si>
-    <t>Fitur Agents Performance Chart adalah untuk menampilkan data performa agen dalam bentuk grafik. Kamu bisa lihat rata-rata waktu penanganan, rata-rata waktu respons, dan jumlah chat yang diterima dari setiap channel. Data disajikan dalam bentuk bar chart untuk jumlah chat dan line chart untuk rata-rata waktu penanganan dan respons. Laporan ini bisa diunduh dalam berbagai format seperti CSV, Excel, PNG, SVG, PDF, JPEG, dan JPG. Jadi, kamu bisa pilih format yang paling sesuai buat kebutuhan kamu.</t>
+    <t>Berapa banyak agent yang dibutuhkan jika terdapat beberapa skenario voicebot?</t>
   </si>
   <si>
-    <t>Apa itu performance Chart Interval pada menu Report di fitur Agent?</t>
+    <t>Apakah platform ailoov bisa diintegrasikan dengan API milik client?</t>
   </si>
   <si>
-    <t>Fitur Agents Performance Chart Interval adalah untuk menampilkan laporan yang hampir sama dengan Agent Performance Chart, namun lebih menekankan pada kinerja agen dalam jangka waktu tertentu. Di sini, kamu dapat melihat rincian seperti rata-rata waktu untuk membalas pesan, rata-rata waktu dalam menyelesaikan percakapan, serta jumlah chat di setiap channel. Sama seperti sebelumnya, data ditampilkan dalam bentuk bar chart dan line chart, dan dapat diunduh dalam berbagai format sesuai kebutuhan.</t>
+    <t>Apakah tersedia fitur transcript call untuk memantau percakapan antara agent dan user?</t>
   </si>
   <si>
-    <t>Apa itu Average Response Time Agent pada menu Report di fitur Agent?</t>
+    <t>Apakah ada fitur cloning agent untuk menduplikasi agent dengan persona yang sama?</t>
   </si>
   <si>
-    <t>Fitur Average Response Time Agent adalah untuk menghitung rata-rata waktu respons pertama dari semua tiket yang ditangani oleh setiap agen, kemudian membaginya berdasarkan jumlah agen yang menangani tiket pada tanggal yang dipilih.</t>
+    <t>Apakah voicebot bisa memberikan promosi backup yang disesuaikan dengan kondisi user?</t>
   </si>
   <si>
-    <t>Apa itu Average Handle Time Agent pada menu Report di fitur Agent?</t>
+    <t>Apakah koreksi ucapan user bisa terekam di reporting voicebotika?</t>
   </si>
   <si>
-    <t>Fitur Average Handle Time Agent adalah untuk mengukur rata-rata waktu penanganan tiket oleh agen, dibagi berdasarkan jumlah agen yang menangani tiket sesuai dengan tanggal yang dipilih.</t>
+    <t>Sejauh mana persona dan alur percakapan voicebot bisa dikustomisasi per skenario?</t>
   </si>
   <si>
-    <t>Apa itu menu Duration pada fitur Report pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Duration Report di OmniBotika V1 menampilkan laporan durasi aktivitas agen dalam dua jenis:
-1) Count Duration – menunjukkan total dan rata-rata durasi status agen (online, idle, dll).
-2) Duration Detail – menampilkan durasi status agen per hari.
-Kedua laporan bisa difilter berdasarkan tanggal dan agen, serta diunduh dalam format CSV atau Excel untuk analisis kinerja yang lebih efisien.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Visitor pada fitur Report pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Visitor Report di OmniBotika menampilkan data pengunjung yang berinteraksi dengan agen di berbagai channel. Kamu bisa lihat jumlah New Visitors, Returning Visitors, dan Unique Visitors untuk memahami pola interaksi dan tingkat engagement, sehingga pengelolaan komunikasi jadi lebih efektif.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Messages pada fitur Report pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Messages di Report OmniBotika V1 menampilkan laporan pesan masuk dan keluar beserta channel yang digunakan. Fitur ini membantu kamu menganalisis aktivitas komunikasi dan memastikan semua pesan tertangani dengan baik untuk menjaga efektivitas tim.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Download Report pada fitur Report pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Download Report di OmniBotika V1 berfungsi untuk mengunduh laporan aktivitas agen seperti total tiket yang ditangani, rata-rata waktu respon, dan waktu penyelesaian. Kamu dapat memilih periode tanggal tertentu dan mengunduh data dalam format CSV atau Excel, sehingga memudahkan dalam memantau dan mengevaluasi kinerja agen secara menyeluruh.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara membuat Artikel pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Berikut cara membuat artikel di OmniBotika V1 : 
-1) Buka menu New Article
-Klik tombol New Article di pojok kanan atas untuk mulai membuat artikel baru.
-2) Isi detail artikel
-Lengkapi Article Properties (kategori, subkategori, tag, gambar, dan excerpt), lalu tambahkan judul dan isi artikel.
-3) Simpan atau publikasikan
-Pilih Save untuk menyimpan, Save as Draft untuk versi draf, atau Publish untuk menerbitkan artikel ke pengguna.</t>
-  </si>
-  <si>
-    <t>Apa itu fitur Setting pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Fifut setting pada Ombibotika V1 yaitu fitur yang digunakan untuk mengatur atau mengontrol banyak hal yang berhubungan dengan operasional dan akses dalam sistem.
-Beberapa hal yang bisa di setting antara lain : 
-1) Timework
-2) SLA
-3) Timezone
-4) Ticket &amp; Routing
-5) Grant Access
-6) Member
-7) Departement
-8) Channel
-9) Personalized Custom Message
-10) Personalization
-11) Shortcut Messages
-12) Skill</t>
-  </si>
-  <si>
-    <t>Apa itu menu SLA pada fitur Setting di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu "SLA" pada fitur Setting di Omnibotika V1 digunakan untuk mengatur jaminan tingkat pelayanan agent kepada customer. SLA agent merupakan acuan untuk melihat seberapa cepat agent dalam merespon dan menghandle customer.
-Berikut langkah-langkah untuk melakukan setting SLA : 
-1) Buka menu "Setting", lalu pilih dan klik "SLA".
-2) Pilih salah satu opsi berikut:
-- "SLA OFF" untuk menonaktifkan SLA.
-- "Default SLA Policy" untuk menggunakan kebijakan bawaan, lalu klik ikon pensil (edit) jika ingin mengubah pengaturannya.
-- "+ SLA Policies" untuk menambahkan kebijakan SLA baru dengan mengisi nama SLA, deskripsi, Channels (biarkan kosong untuk default), serta menentukan SLA target berupa waktu respond dan resolve untuk tiap prioritas.
-3) Tekan "Save".</t>
-  </si>
-  <si>
-    <t>Bagaimana cara setting Ticket Category pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Cara untuk melakukan setting Ticket Category pada Omnibotika V1 adalah sebagai berikut :
-1) Pada menu Setting "Ticket &amp; Routing" pilih bagian "Category".
-2) Pilih setting untuk Ticket Category sebagai berikut : 
-- "+ Add Category" untuk menambah kategori baru
-- tombol "Icon pensil" untuk edit category yang ada
-- tombol "Icon tempat sampah" untuk menghapus category yang ada
-3) Klik "Save" untuk menyimpan, atau klik "Confirm" untuk mengkonfirmasi.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara setting Ticket Tags pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Cara untuk melakukan setting Ticket Tags pada Omnibotika V1 adalah sebagai berikut :
-1) Pada menu Setting "Ticket &amp; Routing" pilih bagian "Tags".
-2) Pilih setting untuk Ticket Tags sebagai berikut : 
-- "+ Add Tags" untuk menambah tag baru
-- tombol "Icon pensil" untuk edit tag yang ada
-- tombol "Icon tempat sampah" untuk menghapus tag yang ada
-3) Klik "Save" untuk menyimpan, atau klik "Confirm" untuk mengkonfirmasi.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara membatasi akses untuk tiap role pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Cara untuk cara membatasi akses untuk tiap role pada Omnibotika V1 adalah sebagai berikut :
-1) Pada menu Setting "Grant Access" pilih bagian Role dengan klik "Setting My Role".
-2) Pada list role, klik ikon titik tiga di sebelah kanan dan klik edit.
-3) Ceklis untuk memberikan akses pada kotak list “As user i can” atau Uncheck untuk menghilangkah akses. Klik "Save" untuk menyimpan.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara menetapkan atau mengubah role ke agent pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Cara menetapkan atau mengubah role ke agent pada Omnibotika V1 adalah sebagai berikut :
-1) Pada menu Setting "Grant Access" pilih bagian Arrange My Member Roles dengan klik "Setting My Role".
-2) Pada tabel list user access, klik tombol "Action" dan pilih "Update Access".
-3) Pilih role yang akan di assign ke user. Klik tombol "Change".</t>
-  </si>
-  <si>
-    <t>Apa itu menu Member pada fitur Setting di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu "Member" pada fitur Setting di OmniBotika V1 adalah tempat untuk melihat dan mengelola daftar akun yang tergabung dalam workspace. Di menu ini, kamu bisa memantau status akun (aktif atau tidak) serta status aktivitas mereka (online atau offline).
-Dalam menu ini terdapat beberapa bagian yaitu :
-- Tabel member : menampilkan daftar member workspace.
-- Table pending member : menampilkan daftar member yang masih pending untuk konfirmasi email invitation.
-- Slots and Remaining Slots Agent : menampilkan seberapa banyak Agent dari segi Total, Used seats, &amp; Remaining seats</t>
-  </si>
-  <si>
-    <t>Bagaimana cara menambahkan member pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Cara menambah member pada Omnibotika V1 adalah sebagai berikut :
-1) Pada menu Setting "Member" klik tombol "Add Member".
-2) Masukkan email member, kemudian klik tombol "Invite".
-3) Email invitation akan terkirim ke email terkait.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Departemen pada fitur Setting di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Department pada fitur Setting di OmniBotika V1 berfungsi untuk mengelompokkan agen berdasarkan divisi atau bidang spesialisasi. Kamu bisa membuat departemen baru, menambahkan deskripsi, serta mengatur anggota di dalamnya. Melalui menu ini, pengelolaan tim menjadi lebih terstruktur dan efisien sesuai dengan tanggung jawab masing-masing.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Channel pada fitur Setting di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Channel di Omnibotika V1 adalah tempat untuk mengatur dan menyambungkan berbagai saluran komunikasi yang kamu pakai, seperti email atau pesan chat. Misalnya, kamu bisa menambahkan akun Gmail supaya pesan yang masuk bisa langsung dikelola dari Omnibotika, tanpa perlu buka banyak aplikasi. Jadi, semua komunikasi bisa dikontrol dari satu tempat dengan cara yang lebih mudah dan praktis.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Personalized Custom Message pada fitur Setting di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Personalized Custom Message di Omnibotika V1 adalah fitur yang memungkinkan kamu mengatur pesan otomatis dari bot ketika agen sedang offline atau sibuk. Dengan fitur ini, pengguna tetap mendapatkan respon yang sopan dan informatif, meskipun belum bisa langsung dibalas oleh agen.
-Contohnya, kamu bisa menulis pesan seperti “Terima kasih sudah menghubungi kami. Saat ini agen sedang tidak tersedia, pesan kamu akan segera kami tanggapi.”
-Cara mengatur Personalized Custom Message:
-1) Buka menu Setting, lalu pilih Custom Message.
-2) Aktifkan opsi Personalized Custom Message.
-3) Isi pesan sesuai kebutuhan, lalu klik Update untuk menyimpan.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Personalization pada fitur Setting di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Personalization di Omnibotika V1 adalah fitur yang berfungsi untuk mengubah nama dan deskripsi workspace agar sesuai dengan kebutuhan atau identitas tim kamu. Dengan fitur ini, workspace bisa terlihat lebih personal dan mencerminkan branding perusahaan.
-Cara mengatur Personalization:
-1) Buka menu Setting, lalu pilih Personalized.
-2) Klik ikon pensil untuk mengedit nama atau deskripsi workspace.
-3) Tekan Save untuk menyimpan perubahan.
-Dengan begitu, tampilan workspace kamu akan lebih mudah dikenali dan terasa lebih profesional.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Shortcut Messages pada fitur Setting di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Shortcut Messages di Omnibotika V1 adalah fitur yang membantu mengirim pesan lebih cepat dengan menggunakan template pesan yang sudah disiapkan sebelumnya. Jadi, agent tidak perlu mengetik ulang pesan yang sering digunakan — tinggal pilih shortcut-nya saja.
-Cara membuat Shortcut Message:
-1) Buka menu Setting, lalu pilih Shortcut Message.
-2) Klik tombol New Shortcut untuk membuat pesan baru.
-3) Isi nama shortcut, pilih siapa yang bisa menggunakannya, tambahkan pesan yang diinginkan, lalu tekan Save.
-Dengan fitur ini, proses membalas pesan pelanggan jadi lebih cepat dan efisien.</t>
-  </si>
-  <si>
-    <t>Apa itu menu Skill pada fitur Setting di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Menu Skill di Omnibotika V1 digunakan untuk mengatur kemampuan atau tanggung jawab agen dalam menangani tiket. Fitur ini membantu memastikan setiap agen hanya menerima tiket dari channel yang sesuai dengan keahliannya, sehingga pekerjaan jadi lebih terarah dan efisien.
-Cara mengatur Skill Agen:
-1) Buka menu Setting, lalu klik Skill.
-2) Pilih agen yang ingin diatur, kemudian klik Skill Routing.
-3) Tentukan pengaturan skill: All Channel, Specific Channel, atau Disable Skill Routing, lalu tekan Save.
-Dengan fitur ini, tim bisa mengatur pembagian tugas agen dengan lebih rapi dan sesuai kebutuhan operasional.</t>
-  </si>
-  <si>
-    <t>Apa itu SLA Out di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>SLA OUT merupakan informasi mengenai ticket yang terlanggar dan tidak sesuai dengan SLA yang telah ditetapkan</t>
-  </si>
-  <si>
-    <t>Dimana kita bisa melihat notifikasi yang masuk ke Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Kamu bisa melihat notifikasi yang masuk langsung dari dashboard Omnibotika v1. Biasanya, notifikasi muncul di bagian atas layar atau di sidebar sesuai pengaturan tampilan sistem.
-Supaya semua notifikasi bisa muncul dengan lancar, pastikan juga izin notifikasi di browser kamu sudah aktif. Dengan begitu, kamu nggak akan ketinggalan informasi penting dari aktivitas yang terjadi di akun Omnibotika kamu.</t>
-  </si>
-  <si>
-    <t>Apa fungsi button "Create Ticket" pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Tombol “Create Ticket” di Omnibotika V1 berfungsi untuk membuat tiket baru secara manual. Fitur ini digunakan ketika ada keluhan, pertanyaan, atau permintaan dari pengguna yang perlu dicatat dan ditangani oleh tim, namun fitur ini hanya dapat berfungsi pada channel Email.
-Dengan menekan tombol ini, agen dapat langsung memasukkan detail masalah agar tercatat dalam sistem. Setiap tiket yang dibuat membantu tim dalam memantau progres, memberikan solusi yang tepat, dan memastikan tidak ada keluhan yang terlewat.
-Secara sederhana, fitur ini membantu mengatur dan menindaklanjuti semua laporan pelanggan dengan lebih rapi dan efisien.</t>
-  </si>
-  <si>
-    <t>Apa saja status Ticket yang terdapat pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Di Omnibotika V1, tiket punya tiga status utama yang menunjukkan tahap penanganannya:
-1) New, tiket baru dibuat dan belum ditangani oleh agen mana pun.
-2) Open, tiket sedang aktif dikerjakan atau dibalas oleh agen.
-3) Solved, tiket sudah selesai ditangani dan dinyatakan tuntas.
-Dengan adanya status ini, tim bisa lebih mudah memantau progres setiap tiket dan memastikan semua laporan pelanggan ditangani sampai selesai.</t>
-  </si>
-  <si>
-    <t>Apa yang terjadi jika Ticket tidak direspon oleh Agent di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Kalau tiket tidak direspon oleh agen dalam waktu 24 jam, tiket tersebut akan otomatis masuk ke kategori Abandoned Tickets. Artinya, tiket masih berstatus New dan belum ada agen yang ditugaskan untuk menanganinya.
-Karena itu, penting bagi agen untuk segera merespon tiket supaya tidak ada laporan pelanggan yang terabaikan dan setiap pengguna bisa mendapatkan solusi dengan cepat dan tepat waktu.</t>
-  </si>
-  <si>
-    <t>Apa saja Priority yang terdapat pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Di OmniBotika v1, setiap tiket bisa diberi label prioritas untuk membantu menentukan tingkat urgensi penanganannya. Prioritas ini juga berkaitan dengan Service Level Agreement (SLA) agar penyelesaian tiket lebih terukur dan efisien. Berikut jenis-jenis prioritas yang biasanya digunakan:
-1) Low Untuk masalah ringan yang tidak terlalu mendesak dan bisa ditangani nanti.
-2) Medium, Untuk masalah yang perlu diperhatikan segera, tapi belum termasuk darurat.
-3) High, Untuk masalah penting yang butuh penanganan cepat agar tidak mengganggu operasional.
-4) Urgent, Untuk masalah yang sangat mendesak dan harus segera diselesaikan karena bisa berdampak besar kalau ditunda.
-Dengan mengatur prioritas ini, agen bisa menentukan urutan kerja lebih efisien dan memastikan pelanggan mendapatkan respon sesuai tingkat urgensinya.</t>
-  </si>
-  <si>
-    <t>Apakah Omnibotika V1 bisa diintegrasikan dengan produk Botika lainnya?</t>
-  </si>
-  <si>
-    <t>Tentu bisa! Omnibotika V1 dapat diintegrasikan dengan produk Botika lain seperti Platform V2 dan Platform V3. Karena Omnibotika berfungsi sebagai layanan untuk live agent, integrasi ini memungkinkan chatbot dari Platform V2 atau V3 untuk meneruskan percakapan pengguna ke agen langsung jika dibutuhkan.
-Jadi, ketika pengguna membutuhkan bantuan manusia setelah berinteraksi dengan chatbot, sistem akan otomatis membuat tiket di Omnibotika agar percakapan bisa dilanjutkan oleh live agent dengan mudah dan terhubung secara real-time.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara mengintegrasikan Omnibotika V1 dengan Platform V2?</t>
-  </si>
-  <si>
-    <t>Tentu bisa banget! Omnibotika V1 dapat diintegrasikan dengan Platform V2 dari Botika untuk memudahkan pengaturan alur komunikasi antara chatbot dan live agent. Integrasi ini memungkinkan chatbot yang dibuat di Platform V2 untuk secara otomatis membuat tiket di Omnibotika ketika pengguna membutuhkan bantuan dari agen manusia.
-Caranya pun sederhana — integrasi dilakukan melalui rule di Platform V2, di mana chatbot akan “jump and run” ke rule Helpdesk Ticketing. Begitu rule ini dijalankan, sistem akan otomatis membuat tiket di Omnibotika sehingga pengguna bisa langsung terhubung dengan live agent tanpa perlu berpindah platform.</t>
-  </si>
-  <si>
-    <t>Apakah kita bisa membalas pesan setelah Agent melakukan End Chat di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Jika chat sudah diakhiri dengan tombol “End Chat”, tiket dianggap selesai. Namun, kamu tetap bisa menghubungi pelanggan lewat fitur “Follow Up” atau channel lain yang terhubung.</t>
-  </si>
-  <si>
-    <t>Apa yang harus dilakukan jika agen belum selesai membalas chat di Chat Console tetapi sudah terlanjur menekan tombol “End Chat”?</t>
-  </si>
-  <si>
-    <t>Jika tombol “End Chat” sudah terlanjur ditekan sebelum chat selesai, kamu bisa mencoba langkah berikut:
-- Re-Open Ticket – Buka kembali tiket yang sudah ditutup; tiket yang ditutup kurang dari 24 jam biasanya masih bisa diakses.
-- Follow Up – Untuk chat dari webchat, gunakan tombol Follow Up untuk menghubungi pelanggan via email.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara Assign Ticket ke Agent?</t>
-  </si>
-  <si>
-    <t>Cara Assign Ticket ke Agent, ada dua cara:
-1. Lewat Menu Tickets:
-- Klik kolom Depart / Agent.
-- Pilih Departement untuk menugaskan ke departemen atau Agent untuk menugaskan langsung ke agen tertentu.
-- Pilih agen yang diinginkan, lalu klik Update untuk menyimpan.
-2. Lewat Chat Console:
-- Buka percakapan yang ingin ditugaskan, lalu klik Edit Info.
-- Masuk ke tab Ticket, klik kotak Assign to, dan pilih Departement atau Agent.
-- Pilih agen yang dituju, lalu klik Update untuk menyimpan perubahan.</t>
-  </si>
-  <si>
-    <t>Apa itu Average Handle Time pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Average Handle Time (AHT) di OmniBotika V1 adalah waktu rata-rata yang dibutuhkan agen untuk menyelesaikan tiket, dihitung sejak agen mulai berinteraksi hingga tiket berstatus Solved. AHT digunakan sebagai indikator efisiensi kerja agen dan dapat dilihat di menu Report untuk analisis kinerja.</t>
-  </si>
-  <si>
-    <t>Apakah pada Omnibotika V1 terdapat paket premium yang dapat dibeli?</t>
-  </si>
-  <si>
-    <t>Di OmniBotika V1 hanya tersedia satu jenis paket yaitu Enterprise yang ditujukan khusus untuk kebutuhan Business to Business (B2B). Untuk informasi lebih lanjut mengenai detail paket kamu dapat menghubungi tim dukungan di support@botika.online.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara edit profile pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Anda bisa edit profile pada Omnibotika V1 dengan cara sebagai berikut :
-1) Klik icon circle di kanan atas dashboard, klik "Profile"
-2) Kemudian Anda akan diarahkan ke halaman yang berisikan informasi mengenai akun Omnibotika Anda. Tekan tombol "Edit".
-3) Anda bisa edit Name, Username, Email, Phone maupun update Password. Jika sudah selesai maka klik "Save" untuk menyimpan perubahan.</t>
-  </si>
-  <si>
-    <t>Apa itu halaman Profile pada Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Halaman profile pada Omnibotika V1 berisi informasi akun Omnibotika Anda. 
-Langkah untuk melihat profil pada dashboard Omnibotika V1, ikuti langkah langkah berikut :
-1) Klik icon circle di kanan atas dashboard, klik "Profile"
-2) Kemudian Anda akan diarahkan ke halaman yang berisikan informasi mengenai akun Omnibotika Anda.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara logout dari Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Untuk menjaga keamanan, Anda bisa keluar dari akun setelah selesai menggunakan Omnibotika V1. Berikut langkahnya :
-1) Klik icon circle pada kanan atas dashboard. 
-2) Pilih dan klik "Logout". 
-3) Sistem akan mengeluarkan Anda dari dashboard dengan aman.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara integrasi Google Play di Omnibotika V1?</t>
-  </si>
-  <si>
-    <t>Dengan integrasi Google Play, Anda dapat menghubungkan aplikasi Anda secara resmi dan aman ke platform Google Play. Untuk melakukannya, diperlukan Client ID dan Client Secret sebagai identitas aplikasi Anda. Kedua data ini bisa Anda dapatkan melalui Google API Console dengan cara membuat proyek baru, mengaktifkan layanan yang dibutuhkan, dan mengatur izin akses (OAuth 2.0). Setelah proses selesai, Anda akan menerima Client ID dan Client Secret yang digunakan untuk memastikan koneksi antara aplikasi dan Google Play berjalan dengan aman.
-Berikut langkahnya:
-1) Masuk ke menu Setting &gt; Channel, lalu klik tombol "+" dan pilih Google Play.
-2) Masukkan client ID, client secret, app link, code yang sebelumnya sudah dibuat melalui link berikut : https://console.cloud.google.com/
-3) Berikan akses pada akun, kemudian klik "Integrate".
-Untuk detail cara integrasi dapat mengikuti link : https://omni.botika.online/help-center/integrations/googleplay.html</t>
-  </si>
-  <si>
-    <t>KB Omnibotika V1</t>
-  </si>
-  <si>
-    <t>Apa itu Voicebotika?</t>
-  </si>
-  <si>
-    <t>Voicebotika Apps adalah aplikasi yang tersedia dalam versi Android yang dirancang untuk penggunaan di smartphone, dan juga tersedia sebagai platform berbasis web yang dapat diakses melalui browser. Di dalamnya, tersedia teknologi Text-to-Speech (TTS) dan Speech-to-Text (STT), sedangkan fitur asisten virtual berbasis AI bernama Selena hanya tersedia di versi Android.
-Dengan TTS, Anda bisa mengubah teks menjadi suara yang terdengar alami. Dengan STT, Anda bisa mengubah rekaman suara menjadi teks yang mudah disalin, diunduh, atau dibagikan. Selena sendiri dapat merespons percakapan sehari-hari baik lewat suara maupun teks.
-Aplikasi ini bermanfaat untuk berbagai kebutuhan, seperti notifikasi kustom, pembacaan e-book, pembuatan nada dering unik, hingga pencatatan suara otomatis.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara atur pengingat Google Calendar dengan Voicebotika?</t>
-  </si>
-  <si>
-    <t>Cara Mengatur Pengingat Google Calendar di Voicebotika APPS
-Dengan Voicebotika APPS, Anda bisa membuat pengingat acara di Google Calendar jadi lebih personal menggunakan suara kustom. Notifikasi bisa dibuat dari teks yang diubah menjadi suara, unggahan audio, atau suara bawaan dari galeri. Berikut langkah-langkahnya:
-1) Buka Set Notif dan aktifkan Atur Pengingat (Google Calendar) dan beri izin akses kalender &amp; notifikasi.
-2) Pilih bahasa &amp; suara (TTS/Galeri/Upload), lalu tentukan durasi pengingat sebelum acara, misalnya 15 menit.
-3) Tekan Simpan. Voicebotika akan memutar notifikasi kustom sebelum acara sesuai pengaturan Anda.
-Catatan: Pastikan izin sinkronisasi kalender dan notifikasi sudah diaktifkan agar pengingat bisa berfungsi dengan baik.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara menghubungi customer support Voicebotika?</t>
-  </si>
-  <si>
-    <t>Cara Menghubungi Tim Dukungan Voicebotika APPS 
-Jika Anda mengalami kendala atau memiliki pertanyaan, Anda dapat langsung menghubungi tim support melalui WhatsApp. Berikut langkah-langkahnya: 
-1) Masuk ke menu Help, lalu pilih Hubungi Kami. 
-2) Maka akan tersedia opsi untuk menghubungi support via WhatsApp 
-3) Lalu isi pertanyaan atau kendala Anda. Tim dukungan akan membalas sesuai jalur komunikasi yang dipilih.</t>
-  </si>
-  <si>
-    <t>Apakah hasil TTS bisa dibagikan ke WhatsApp?</t>
-  </si>
-  <si>
-    <t>Ya, hasil TTS di Voicebotika APPS bisa langsung dibagikan ke WhatsApp. Fitur ini memudahkan Anda untuk mengirim audio ke teman, keluarga, atau rekan kerja tanpa perlu menyimpannya terlebih dahulu. Berikut caranya: 
-1) Setelah generate, pilih opsi Share. 
-2) Pilih aplikasi WhatsApp. 
-3) Pilih kontak atau grup tujuan, lalu kirim.</t>
-  </si>
-  <si>
-    <t>KB Voicebotika APP</t>
-  </si>
-  <si>
-    <t>Bisakah nomor pribadi dipakai untuk WhatsApp Business di WABIS?</t>
-  </si>
-  <si>
-    <t>Bisa, asalkan nomor belum terdaftar di WhatsApp Business API. Namun, disarankan memakai nomor khusus bisnis agar komunikasi lebih profesional dan tidak tercampur dengan chat pribadi. Contoh: pemilik toko online awalnya pakai nomor pribadi, lalu ganti ke nomor bisnis agar lebih rapi.</t>
-  </si>
-  <si>
-    <t>Apakah nomor WhatsApp yang dipakai di WABIS bisa diganti?</t>
-  </si>
-  <si>
-    <t>Nomor WhatsApp di WABIS tidak bisa diganti langsung. Jika ingin menggunakan nomor lain, Anda perlu menambahkan nomor baru, lalu melakukan integrasi dan verifikasi ulang agar bisa digunakan di sistem. Proses ini memerlukan bantuan dari tim support Botika, jadi silakan hubungi support@botika.online untuk melakukan perubahan.</t>
-  </si>
-  <si>
-    <t>Apa saja data yang bisa dilihat di Insight?</t>
-  </si>
-  <si>
-    <t>Insight menampilkan: 
-- Jumlah Message Templates 
-- Jumlah Phone Numbers 
-- Jumlah Broadcast 
-- Total Contacts 
-- Overall Message Usage dalam periode waktu tertentu (misalnya, "Last 1 Hours") 
-- Total pesan Sent (Terkirim) 
-- Total pesan Delivered (Diterima) 
-- Total pesan Read (Terbaca) 
-- Total pesan Failed (Gagal)</t>
-  </si>
-  <si>
-    <t>KB WABIS</t>
-  </si>
-  <si>
-    <t>Bot di Botmaster dapat diintegrasikan dengan channel apa saja?</t>
-  </si>
-  <si>
-    <t>Di Botmaster, bot kamu bisa diintegrasikan dengan berbagai macam channel, lho! Berikut adalah beberapa channel yang bisa kamu pilih : 
-1. Email – Bot dapat mengirim dan menerima pesan melalui email. 
-2. Facebook Comment – Bot dapat membalas komentar di postingan Facebook Page. 
-3. Facebook Messenger – Bot dapat berinteraksi melalui pesan langsung, tidak mendukung group chat. 
-4. Instagram Comment – Bot bisa membalas komentar di postingan Instagram. 
-5. Instagram DM – Bot bisa merespons pesan langsung (DM). 
-6. Kakao Talk – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-7. Line – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-8. Telegram – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-9. Viber – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-10. WeChat – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-11. Zalo – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-12. Telepon – Bot dapat diintegrasikan untuk interaksi via panggilan suara. 
-13. Twitter – Bot bisa merespons mention atau DM, tidak untuk group atau tweet thread otomatis. 
-14. Twitter Comment – Bot dapat membalas komentar di tweet. 
-15. Web Chat – Bot bisa diakses langsung melalui widget web di situs kamu. 
-16. Webhook – Digunakan untuk integrasi custom dengan sistem lain. 
-17. WhatsApp Official – Bot dapat digunakan melalui akun WhatsApp Business API, tidak mendukung percakapan di grup. 
-18. Google Play – Dapat diintegrasikan sesuai fungsi masing-masing platform (misalnya Teams untuk percakapan internal). 
-19. Microsoft Outlook – Dapat diintegrasikan sesuai fungsi masing-masing platform (misalnya Teams untuk percakapan internal). 
-20. Microsoft Teams – Dapat diintegrasikan sesuai fungsi masing-masing platform (misalnya Teams untuk percakapan internal). 
-Dengan banyaknya pilihan channel tersebut, kamu bisa memperluas jangkauan chatbot dan memastikan bahwa pesanmu sampai ke lebih banyak orang.</t>
-  </si>
-  <si>
-    <t>Bot di Botmaster dapat diintegrasikan dengan channel media sosial mana saja?</t>
-  </si>
-  <si>
-    <t>Wah, rencana kamu keren banget! Di Botmaster, bot yang kamu buat bisa diintegrasikan ke berbagai channel. Berikut beberapa channel yang bisa kamu gunakan: 
-1) Email – Bot dapat mengirim dan menerima pesan melalui email. 
-2) Facebook Comment – Bot dapat membalas komentar di postingan Facebook Page. 
-3) Facebook Messenger – Bot dapat berinteraksi melalui pesan langsung, tidak mendukung group chat. 
-4) Instagram Comment – Bot bisa membalas komentar di postingan Instagram. 
-5) Instagram DM – Bot bisa merespons pesan langsung (DM). 
-6) Kakao Talk – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-7) Line – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-8) Telegram – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-9) Viber – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-10) WeChat – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-11) Zalo – Bot bisa berkomunikasi lewat pesan pribadi, tidak melalui grup. 
-12) Telepon – Bot dapat diintegrasikan untuk interaksi via panggilan suara. 
-13) Web Chat – Bot bisa diakses langsung melalui widget web di situs kamu. 
-14) Webhook – Digunakan untuk integrasi custom dengan sistem lain. 
-15) WhatsApp Official – Bot dapat digunakan melalui akun WhatsApp Business API, tidak mendukung percakapan di grup. 
-16) Google Play – Dapat diintegrasikan sesuai fungsi masing-masing platform (misalnya Teams untuk percakapan internal). 
-17) Microsoft Outlook – Dapat diintegrasikan sesuai fungsi masing-masing platform (misalnya Teams untuk percakapan internal). 
-18) Microsoft Teams – Dapat diintegrasikan sesuai fungsi masing-masing platform (misalnya Teams untuk percakapan internal). 
-Dengan integrasi ini, chatbot kamu bisa menjangkau lebih banyak orang dan memberikan layanan yang lebih luas. Kamu tinggal pilih channel yang diinginkan dari menu integrasi dan ikuti petunjuk yang ada untuk menyelesaikan prosesnya. Jadi, pelanggan kamu bisa berinteraksi dengan bot melalui platform yang mereka suka. Mantap, kan?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KB BOTMASTER </t>
-  </si>
-  <si>
-    <t>Apa yang dimaksud dengan avatar interaktif?</t>
-  </si>
-  <si>
-    <t>Avatar interaktif adalah representasi digital manusia yang dapat merespons pengguna secara real-time, baik melalui wajah virtual, gerakan tubuh, maupun suara. Avatar ini mampu menyesuaikan reaksi seperti tersenyum, mengangguk, dan menggerakkan bibir sesuai suara (lip-sync), sehingga interaksi terasa lebih natural dan seolah berbicara dengan manusia nyata.</t>
-  </si>
-  <si>
-    <t>Apa yang dimaksud dengan LLM Integration pada DHAI?</t>
-  </si>
-  <si>
-    <t>Dengan dukungan Large Language Models (LLM), avatar Digital Human dapat memahami konteks percakapan dengan lebih mendalam, mengenali maksud pengguna, dan menyesuaikan jawaban secara cerdas. Teknologi ini memungkinkan avatar memberikan respon yang relevan, alami, dan fleksibel, sehingga interaksi terasa seperti berbicara dengan manusia yang benar-benar mengerti situasi dan kebutuhan pengguna.</t>
-  </si>
-  <si>
-    <t>Platform apa saja yang kompatibel dengan Digital Human AI?</t>
-  </si>
-  <si>
-    <t>Avatar Digital Human dapat dihadirkan di berbagai platform, mulai dari website, aplikasi mobile, mesin kiosk, hingga layar LCD interaktif. Fleksibilitas ini memungkinkan perusahaan menghadirkan pengalaman interaktif yang konsisten di berbagai kanal, sehingga pengguna dapat berkomunikasi dengan avatar secara mudah dan natural di mana pun mereka berada.</t>
-  </si>
-  <si>
-    <t>Apa yang dimaksud dengan easy embedding?</t>
-  </si>
-  <si>
-    <t>Proses integrasi avatar Digital Human relatif mudah. Untuk website atau aplikasi, biasanya cukup menambahkan skrip atau kode singkat yang disediakan, dan avatar sudah bisa tampil serta berinteraksi dengan pengguna. Pendekatan ini mempermudah perusahaan menghadirkan pengalaman interaktif tanpa perlu melakukan perubahan besar pada sistem yang sudah ada.</t>
-  </si>
-  <si>
-    <t>Bagaimana Digital Human AI digunakan untuk customer service?</t>
-  </si>
-  <si>
-    <t>Digital Human AI dibekali dengan sistem RAG (Retrieval-Augmented Generation) atau Knowledge Base (KB) yang berisi seluruh informasi dan pengetahuan yang biasanya dimiliki oleh tim customer service. Dengan dukungan ini, avatar dapat memberikan jawaban yang akurat, relevan, dan kontekstual terkait layanan yang disediakan perusahaan, sehingga pengalaman pengguna menjadi lebih informatif dan efisien.</t>
-  </si>
-  <si>
-    <t>Faktor apa saja yang memengaruhi akurasi STT pada DHAI?</t>
-  </si>
-  <si>
-    <t>Dalam penggunaan Digital Human AI, akurasi pengenalan suara bisa menurun jika lingkungan terlalu bising, suara pengguna terlalu pelan atau terlalu cepat, atau terdapat logat yang belum dikenali sistem. Untuk hasil terbaik, disarankan berbicara dengan jelas, berada cukup dekat dengan mikrofon, dan jika masih belum terbaca dengan baik, pengguna dapat beralih menggunakan fitur ketik.</t>
-  </si>
-  <si>
-    <t>Apa itu mode publik dengan suara keras?</t>
-  </si>
-  <si>
-    <t>Dalam situasi seperti acara, pameran, atau demo publik, avatar dapat beroperasi dalam mode publik, di mana suara dibuat lebih keras dan ekspresi animasi menjadi lebih hidup serta menarik perhatian. Fitur ini membantu avatar berinteraksi dengan banyak orang sekaligus dan menciptakan pengalaman yang lebih dinamis dan interaktif.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kapan avatar DHAI diperbarui agar tetap sesuai brand dan relevansi? 
-</t>
-  </si>
-  <si>
-    <t>Avatar Digital Human AI diperbarui secara berkala sesuai perubahan identitas merek, gaya komunikasi, atau tampilan perusahaan, agar tetap relevan dan selaras dengan citra perusahaan.</t>
-  </si>
-  <si>
-    <t>Di mana data percakapan antara pengguna dan DHAI disimpan?</t>
-  </si>
-  <si>
-    <t>Data percakapan pada Digital Human AI disimpan secara aman pada server dengan enkripsi, baik melalui layanan cloud maupun sistem on-premise, untuk memastikan kerahasiaan dan perlindungan informasi pengguna.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagaimana pembaruan AI dilakukan untuk tingkatkan akurasi DHAI? 
-</t>
-  </si>
-  <si>
-    <t>Pelatihan Digital Human AI dilakukan dengan menambahkan data percakapan baru serta memperbaiki respons sistem. Model DHAI terus belajar untuk meningkatkan akurasi, memahami konteks, dan mengenali emosi pengguna. Proses pembaruan dilakukan secara berkala untuk memastikan performa avatar tetap optimal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagaimana perusahaan mengukur efektivitas penggunaan DHAI? 
-</t>
-  </si>
-  <si>
-    <t>Efektivitas Digital Human AI diukur melalui data yang tersedia di dashboard, antara lain jumlah interaksi, tingkat kepuasan pengguna, dan persentase pertanyaan yang dapat dijawab tanpa intervensi manusia. Informasi ini digunakan untuk menilai sejauh mana DHAI mampu mempercepat layanan dan meningkatkan kualitas pengalaman pengguna.</t>
-  </si>
-  <si>
-    <t>Apa yang dimaksud dengan persona pada Digital Human AI?</t>
-  </si>
-  <si>
-    <t>Persona pada Digital Human AI merupakan identitas atau karakter unik yang dimiliki oleh avatar, mencakup nama, sifat, gaya bahasa, serta perilaku komunikasi. Elemen ini dirancang agar avatar dapat berinteraksi secara natural dan sesuai dengan tujuan penggunaannya, misalnya sebagai customer service, pelatih digital, atau presenter dalam acara maupun platform digital.</t>
-  </si>
-  <si>
-    <t>Di mana persona DHAI diterapkan agar tetap konsisten di berbagai kanal interaksi?</t>
-  </si>
-  <si>
-    <t>Persona diterapkan di seluruh kanal tempat avatar Digital Human AI beroperasi, seperti website, aplikasi mobile, kiosk interaktif, maupun layar digital. Konsistensi persona di berbagai platform ini membantu menjaga pengalaman pengguna tetap seragam, profesional, dan selaras dengan citra merek.</t>
-  </si>
-  <si>
-    <t>KB DHAI</t>
-  </si>
-  <si>
-    <t>Bagaimana cara mengakhiri sesi percakapan dengan Voicebot?</t>
-  </si>
-  <si>
-    <t>Jika Anda ingin menghentikan percakapan, cukup tekan tombol “End” pada layar Voicebot. Tindakan ini akan menutup sesi dan menghentikan semua respons dari Voicebot.</t>
-  </si>
-  <si>
-    <t>Bisakah Voicebot digunakan untuk layanan pelanggan (customer service)?</t>
-  </si>
-  <si>
-    <t>Ya, Voicebot bisa digunakan untuk layanan pelanggan (customer service). Teknologi ini dapat menjawab pertanyaan umum, memberikan informasi dasar, serta membantu permintaan sederhana seperti pengecekan status, pengingat jadwal, atau konfirmasi data. 
-Selain itu, Voicebot juga bisa digunakan untuk berbagai kebutuhan lain, seperti mengingatkan jadwal atau tagihan, melakukan survei kepuasan, menjadi hotline informasi publik, berperan sebagai asisten pribadi, hingga terintegrasi dengan Digital Human AI untuk pengalaman interaktif di tempat seperti mal atau layanan publik. 
-Dengan dukungan AI Agent dan kemampuan memahami konteks percakapan, Voicebot dapat dihubungkan ke CRM, telepon, dan platform omnichannel, sehingga membantu menciptakan layanan yang cepat, efisien, dan modern.</t>
-  </si>
-  <si>
-    <t>Bagaimana integrasi Voicebot dengan sistem bisnis?</t>
-  </si>
-  <si>
-    <t>Voicebot hanya bisa dipakai di website, dan belum mendukung integrasi langsung dengan aplikasi lain.</t>
-  </si>
-  <si>
-    <t>Apakah percakapan dengan Voicebot bisa direkam?</t>
-  </si>
-  <si>
-    <t>Secara umum, percakapan dengan Voicebot tidak direkam. Namun, jika Voicebot digunakan melalui sistem telephony (panggilan telepon), maka percakapan dapat direkam secara otomatis beserta transkripnya untuk keperluan analisis atau peningkatan kualitas layanan. 
-Semua proses ini mengikuti kebijakan privasi dan keamanan data Botika, sehingga rekaman dan transkrip hanya digunakan untuk tujuan operasional yang sah. 
-Untuk kebutuhan lebih lanjut atau permintaan terkait data percakapan, silakan menghubungi tim support Botika melalui email support@botika.online.</t>
-  </si>
-  <si>
-    <t>Apakah Voicebot bisa diintegrasikan dengan WhatsApp Business API?</t>
-  </si>
-  <si>
-    <t>Bisa. Voicebot dapat diintegrasikan dengan WhatsApp Business API untuk membantu menjawab pesan pelanggan secara otomatis melalui teks maupun suara. Integrasi ini cocok untuk layanan pelanggan, promosi, notifikasi otomatis, dll. 
-Untuk kebutuhan tersebut, kamu dapat menghubungi galuh@botika.online.</t>
-  </si>
-  <si>
-    <t>Apakah Voicebot bisa digunakan untuk pertanyaan matematika?</t>
-  </si>
-  <si>
-    <t>Bisa. Voicebot dapat menjawab pertanyaan matematika seperti perhitungan aritmetika atau konsep matematika umum. Karena input pertanyaan menggunakan suara, disarankan agar pertanyaan diucapkan dengan jelas agar sistem dapat mengenali dan memprosesnya dengan tepat. 
-Untuk soal yang lebih kompleks atau membutuhkan langkah perhitungan mendalam, hasilnya mungkin terbatas, sehingga pengguna tetap disarankan memeriksa jawaban secara manual atau menggunakan alat khusus matematika. 
-Untuk skenario penggunaan matematika yang lebih spesifik atau integrasi dengan sistem edukasi, kamu bisa menghubungi galuh@botika.online.</t>
-  </si>
-  <si>
-    <t>Apakah Voicebot bisa dihubungkan dengan speaker pintar?</t>
-  </si>
-  <si>
-    <t>Jika perangkat yang digunakan mendukung koneksi audio melalui Bluetooth atau kabel, suara Voicebot dapat dialihkan dan diputar lewat speaker eksternal, sehingga percakapan terdengar lebih jelas dan bisa dinikmati oleh beberapa orang sekaligus. Hal ini berguna, misalnya, untuk presentasi, pembelajaran interaktif, atau penggunaan di ruang publik. Pastikan koneksi antara perangkat dan speaker stabil agar suara tetap terdengar dengan baik. 
-Namun, jika yang dimaksud adalah smart speaker seperti Google Nest, Alexa, atau smart speaker lainnya, integrasi langsung belum tersedia. Untuk kebutuhan tersebut, kamu bisa menghubungi galuh@botika.online.</t>
-  </si>
-  <si>
-    <t>Apakah Voicebot bisa menjawab pertanyaan berulang dengan konsisten?</t>
-  </si>
-  <si>
-    <t>Bisa. Voicebot dapat memberikan jawaban yang konsisten untuk pertanyaan yang sama, karena sistem merespons berdasarkan model AI dan data yang tersedia. Namun, konsistensi jawaban bisa dipengaruhi oleh cara pertanyaan diajukan atau konteks percakapan.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara melatih tim CS menggunakan Voicebot?</t>
-  </si>
-  <si>
-    <t>Untuk melatih tim Customer Service menggunakan Voicebot, mulailah dengan memperkenalkan cara kerja Voicebot, termasuk bagaimana menerima pertanyaan dan memberikan jawaban dalam bentuk audio dan teks. Selanjutnya, lakukan simulasi skenario pelanggan dengan berbagai pertanyaan umum agar tim terbiasa melihat respons Voicebot secara real-time. Terakhir, latih tim menggunakan interupsi atau pertanyaan lanjutan untuk mendapatkan jawaban yang lebih tepat dan efisien. 
-Untuk skenario pelatihan yang lebih spesifik atau integrasi langsung ke sistem CS perusahaan, kamu bisa menghubungi galuh@botika.online.</t>
-  </si>
-  <si>
-    <t>Apakah Voicebot bisa diintegrasikan dengan avatar 3D?</t>
-  </si>
-  <si>
-    <t>Bisa. Voicebot dapat diintegrasikan dengan Digital Human AI, sehingga percakapan menjadi lebih interaktif dan menarik secara visual. Avatar ini bisa menggunakan hasil generate AI maupun representasi real human, dengan ekspresi wajah, gerakan, dan respons suara yang menyesuaikan percakapan secara real-time. 
-Integrasi ini cocok digunakan untuk layanan publik, edukasi interaktif, hingga customer service digital. Untuk kebutuhan integrasi dengan DHAI, kamu bisa menghubungi galuh@botika.online.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apakah kita bisa menyesuaian waktu respons Voicebot? 
-</t>
-  </si>
-  <si>
-    <t>Saat ini, Voicebot tidak bisa mengatur kecepatan jawaban secara manual. Waktu respons yang diterima pengguna dapat berbeda-beda tergantung beberapa faktor, seperti kualitas dan stabilitas koneksi internet, panjang pertanyaan, serta beban server saat itu. Dengan koneksi yang stabil, respons biasanya lebih cepat dan lancar, sedangkan jika jaringan lemah, jawaban bisa sedikit tertunda.</t>
-  </si>
-  <si>
-    <t>KB Voicebot</t>
+    <t>omnibotika v2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1782,6 +309,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1835,24 +368,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2182,2651 +715,1355 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="138" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="88" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="175.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="88" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="63" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="63" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="88" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="275.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="372.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="125.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="125.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="248.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="88" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="63" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="5">
-        <v>28</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="5">
-        <v>29</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="B28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="5">
-        <v>30</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="5">
-        <v>31</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="233" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="5">
-        <v>32</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="5">
-        <v>33</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="5">
-        <v>34</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="5">
-        <v>35</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="5">
-        <v>36</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="5">
-        <v>37</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="5">
-        <v>38</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="5">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="5">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="5">
-        <v>41</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="5">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="5">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="5">
-        <v>44</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="5">
-        <v>45</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="5">
-        <v>46</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="5">
-        <v>47</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="5">
-        <v>48</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="5">
-        <v>49</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="5">
-        <v>50</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="5">
-        <v>51</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="5">
-        <v>52</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="5">
-        <v>53</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="5">
-        <v>54</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="5">
-        <v>55</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="5">
-        <v>56</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="5">
-        <v>57</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="5">
-        <v>58</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="5">
-        <v>59</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="5">
-        <v>60</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="357" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="5">
-        <v>61</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="5">
-        <v>62</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="5">
-        <v>63</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="5">
-        <v>64</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="5">
-        <v>65</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="5">
-        <v>66</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="5">
-        <v>67</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="233" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="5">
-        <v>68</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="5">
-        <v>69</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="5">
-        <v>70</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="5">
-        <v>71</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="5">
-        <v>72</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="5">
-        <v>73</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="5">
-        <v>74</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="5">
-        <v>75</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="5">
-        <v>76</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="5">
-        <v>77</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="5">
-        <v>78</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="5">
-        <v>79</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="5">
-        <v>80</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="5">
-        <v>81</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="5">
-        <v>82</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="5">
-        <v>83</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="5">
-        <v>84</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="5">
-        <v>85</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="5">
-        <v>86</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="5">
-        <v>87</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="5">
-        <v>88</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="5">
-        <v>89</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="5">
-        <v>90</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="5">
-        <v>91</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="5">
-        <v>92</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="5">
-        <v>93</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="5">
-        <v>94</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="5">
-        <v>95</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="5">
-        <v>96</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="5">
-        <v>97</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="5">
-        <v>98</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="5">
-        <v>99</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="388" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="5">
-        <v>100</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D101" s="8" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="5">
-        <v>101</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="5">
-        <v>102</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="D103" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="5">
-        <v>103</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="5">
-        <v>104</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="5">
-        <v>105</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D106" s="8" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="5">
-        <v>106</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="D107" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="5">
-        <v>107</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="5">
-        <v>108</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="D109" s="8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="5">
-        <v>109</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="5">
-        <v>110</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="5">
-        <v>111</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="D112" s="8" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="5">
-        <v>112</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="5">
-        <v>113</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="5">
-        <v>114</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="233" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="5">
-        <v>115</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="5">
-        <v>116</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D117" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="5">
-        <v>117</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D118" s="8" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="5">
-        <v>118</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="5">
-        <v>119</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="5">
-        <v>120</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="5">
-        <v>121</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="5">
-        <v>122</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="D123" s="8" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="5">
-        <v>123</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="5">
-        <v>124</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="D125" s="8" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="5">
-        <v>125</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D126" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="5">
-        <v>126</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="D127" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="341.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="5">
-        <v>127</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="5">
-        <v>128</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="5">
-        <v>129</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="D130" s="8" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="5">
-        <v>130</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="5">
-        <v>131</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="D132" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="217.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="5">
-        <v>132</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="D133" s="8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="5">
-        <v>133</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="D134" s="8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="5">
-        <v>134</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="D135" s="8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="5">
-        <v>135</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="D136" s="8" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="279.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="5">
-        <v>136</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D137" s="8" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="264" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="5">
-        <v>137</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="264" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="5">
-        <v>138</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="D139" s="8" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="264" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="5">
-        <v>139</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="5">
-        <v>140</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D141" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="5">
-        <v>141</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D142" s="8" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="217.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="5">
-        <v>142</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D143" s="8" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="217.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="5">
-        <v>143</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="D144" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="5">
-        <v>144</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D145" s="8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="5">
-        <v>145</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D146" s="8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="5">
-        <v>146</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="D147" s="8" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="5">
-        <v>147</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="5">
-        <v>148</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="D149" s="8" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="5">
-        <v>149</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="264" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="5">
-        <v>150</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="D151" s="8" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="5">
-        <v>151</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="D152" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="5">
-        <v>152</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D153" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="5">
-        <v>153</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="5">
-        <v>154</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="D155" s="8" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="5">
-        <v>155</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D156" s="8" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="326" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="5">
-        <v>156</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="113" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="5">
-        <v>157</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="100.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="5">
-        <v>158</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="88" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="5">
-        <v>159</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="63" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="5">
-        <v>160</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="5">
-        <v>161</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C162" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="5">
-        <v>162</v>
-      </c>
-      <c r="B163" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="125.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="5">
-        <v>163</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="288" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="5">
-        <v>164</v>
-      </c>
-      <c r="B165" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="D165" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="313" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="5">
-        <v>165</v>
-      </c>
-      <c r="B166" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="D166" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="5">
-        <v>166</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C167" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="D167" s="9" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="5">
-        <v>167</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C168" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="D168" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="5">
-        <v>168</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C169" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="D169" s="9" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="5">
-        <v>169</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C170" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="D170" s="9" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="5">
-        <v>170</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C171" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="D171" s="9" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="5">
-        <v>171</v>
-      </c>
-      <c r="B172" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C172" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="D172" s="9" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="5">
-        <v>172</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C173" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D173" s="9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="5">
-        <v>173</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C174" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="D174" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="5">
-        <v>174</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C175" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="64" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="5">
-        <v>175</v>
-      </c>
-      <c r="B176" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="5">
-        <v>176</v>
-      </c>
-      <c r="B177" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C177" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="5">
-        <v>177</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C178" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D178" s="9" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="5">
-        <v>178</v>
-      </c>
-      <c r="B179" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C179" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="D179" s="9" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="5">
-        <v>179</v>
-      </c>
-      <c r="B180" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C180" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="D180" s="9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="114" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="5">
-        <v>180</v>
-      </c>
-      <c r="B181" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C181" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="D181" s="9" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="5">
-        <v>181</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C182" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="D182" s="9" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="5">
-        <v>182</v>
-      </c>
-      <c r="B183" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C183" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="D183" s="9" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="5">
-        <v>183</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C184" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="D184" s="9" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" ht="114" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="5">
-        <v>184</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C185" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="D185" s="9" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" ht="89" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="5">
-        <v>185</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="D186" s="9" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="5">
-        <v>186</v>
-      </c>
-      <c r="B187" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C187" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D187" s="9" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="5">
-        <v>187</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C188" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="D188" s="9" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="5">
-        <v>188</v>
-      </c>
-      <c r="B189" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C189" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="D189" s="9" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="5">
-        <v>189</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C190" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="D190" s="9" t="s">
-        <v>390</v>
-      </c>
+      <c r="D28" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+    </row>
+    <row r="42" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+    </row>
+    <row r="43" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+    </row>
+    <row r="46" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+    </row>
+    <row r="47" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+    </row>
+    <row r="48" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+    </row>
+    <row r="49" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="5"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+    </row>
+    <row r="51" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="5"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+    </row>
+    <row r="52" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="5"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+    </row>
+    <row r="53" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="5"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+    </row>
+    <row r="54" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="5"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+    </row>
+    <row r="55" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="5"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+    </row>
+    <row r="56" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="5"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+    </row>
+    <row r="57" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="5"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+    </row>
+    <row r="58" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="5"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+    </row>
+    <row r="59" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="5"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="5"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+    </row>
+    <row r="61" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="5"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="5"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+    </row>
+    <row r="63" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="5"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="5"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="5"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+    </row>
+    <row r="66" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="5"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+    </row>
+    <row r="67" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="5"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+    </row>
+    <row r="68" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="5"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+    </row>
+    <row r="69" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="5"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+    </row>
+    <row r="70" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="5"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+    </row>
+    <row r="71" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="5"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+    </row>
+    <row r="72" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="5"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+    </row>
+    <row r="73" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="5"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="5"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="5"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="5"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+    </row>
+    <row r="77" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="5"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+    </row>
+    <row r="78" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="5"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+    </row>
+    <row r="79" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="5"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+    </row>
+    <row r="80" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="5"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="5"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+    </row>
+    <row r="82" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="5"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+    </row>
+    <row r="83" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="5"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+    </row>
+    <row r="84" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="5"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="5"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="5"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+    </row>
+    <row r="87" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="5"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+    </row>
+    <row r="88" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="5"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+    </row>
+    <row r="89" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="5"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+    </row>
+    <row r="90" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="5"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+    </row>
+    <row r="91" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="5"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+    </row>
+    <row r="92" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="5"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+    </row>
+    <row r="93" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="5"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+    </row>
+    <row r="94" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="5"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+    </row>
+    <row r="95" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="5"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+    </row>
+    <row r="96" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="5"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+    </row>
+    <row r="97" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="5"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+    </row>
+    <row r="98" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="5"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+    </row>
+    <row r="99" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="5"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+    </row>
+    <row r="100" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="5"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+    </row>
+    <row r="101" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="5"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+    </row>
+    <row r="102" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="5"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+    </row>
+    <row r="103" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="5"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+    </row>
+    <row r="104" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="5"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+    </row>
+    <row r="105" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="5"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+    </row>
+    <row r="106" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="5"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+    </row>
+    <row r="107" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="5"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+    </row>
+    <row r="108" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="5"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+    </row>
+    <row r="109" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="5"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+    </row>
+    <row r="110" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="5"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+    </row>
+    <row r="111" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="5"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+    </row>
+    <row r="112" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="5"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+    </row>
+    <row r="113" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="5"/>
+      <c r="B113" s="6"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+    </row>
+    <row r="114" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="5"/>
+      <c r="B114" s="6"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+    </row>
+    <row r="115" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="5"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+    </row>
+    <row r="116" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="5"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+    </row>
+    <row r="117" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="5"/>
+      <c r="B117" s="6"/>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+    </row>
+    <row r="118" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="5"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+    </row>
+    <row r="119" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="5"/>
+      <c r="B119" s="6"/>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+    </row>
+    <row r="120" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="5"/>
+      <c r="B120" s="6"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+    </row>
+    <row r="121" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="5"/>
+      <c r="B121" s="6"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+    </row>
+    <row r="122" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="5"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+    </row>
+    <row r="123" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="5"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+    </row>
+    <row r="124" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="5"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+    </row>
+    <row r="125" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="5"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+    </row>
+    <row r="126" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="5"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+    </row>
+    <row r="127" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="5"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+    </row>
+    <row r="128" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="5"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+    </row>
+    <row r="129" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="5"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+    </row>
+    <row r="130" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="5"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+    </row>
+    <row r="131" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="5"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+    </row>
+    <row r="132" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="5"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+    </row>
+    <row r="133" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="5"/>
+      <c r="B133" s="6"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+    </row>
+    <row r="134" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="5"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+    </row>
+    <row r="135" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="5"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+    </row>
+    <row r="136" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="5"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+    </row>
+    <row r="137" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="5"/>
+      <c r="B137" s="6"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+    </row>
+    <row r="138" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="5"/>
+      <c r="B138" s="6"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+    </row>
+    <row r="139" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="5"/>
+      <c r="B139" s="6"/>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+    </row>
+    <row r="140" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="5"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+    </row>
+    <row r="141" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="5"/>
+      <c r="B141" s="6"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+    </row>
+    <row r="142" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="5"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+    </row>
+    <row r="143" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="5"/>
+      <c r="B143" s="6"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+    </row>
+    <row r="144" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="5"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="7"/>
+      <c r="D144" s="7"/>
+    </row>
+    <row r="145" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="5"/>
+      <c r="B145" s="6"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+    </row>
+    <row r="146" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="5"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+    </row>
+    <row r="147" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="5"/>
+      <c r="B147" s="6"/>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+    </row>
+    <row r="148" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="5"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+    </row>
+    <row r="149" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="5"/>
+      <c r="B149" s="6"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+    </row>
+    <row r="150" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A150" s="5"/>
+      <c r="B150" s="6"/>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+    </row>
+    <row r="151" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="5"/>
+      <c r="B151" s="6"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+    </row>
+    <row r="152" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A152" s="5"/>
+      <c r="B152" s="6"/>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+    </row>
+    <row r="153" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A153" s="5"/>
+      <c r="B153" s="6"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+    </row>
+    <row r="154" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A154" s="5"/>
+      <c r="B154" s="6"/>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+    </row>
+    <row r="155" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A155" s="5"/>
+      <c r="B155" s="6"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+    </row>
+    <row r="156" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="5"/>
+      <c r="B156" s="6"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+    </row>
+    <row r="157" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="5"/>
+      <c r="B157" s="6"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+    </row>
+    <row r="158" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="5"/>
+      <c r="B158" s="6"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+    </row>
+    <row r="159" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="5"/>
+      <c r="B159" s="6"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+    </row>
+    <row r="160" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="5"/>
+      <c r="B160" s="6"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+    </row>
+    <row r="161" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A161" s="5"/>
+      <c r="B161" s="6"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+    </row>
+    <row r="162" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A162" s="5"/>
+      <c r="B162" s="6"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+    </row>
+    <row r="163" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A163" s="5"/>
+      <c r="B163" s="6"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+    </row>
+    <row r="164" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="5"/>
+      <c r="B164" s="6"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+    </row>
+    <row r="165" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="5"/>
+      <c r="B165" s="6"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+    </row>
+    <row r="166" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="5"/>
+      <c r="B166" s="6"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+    </row>
+    <row r="167" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="5"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="8"/>
+    </row>
+    <row r="168" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="5"/>
+      <c r="B168" s="6"/>
+      <c r="C168" s="8"/>
+      <c r="D168" s="8"/>
+    </row>
+    <row r="169" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="5"/>
+      <c r="B169" s="6"/>
+      <c r="C169" s="8"/>
+      <c r="D169" s="8"/>
+    </row>
+    <row r="170" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A170" s="5"/>
+      <c r="B170" s="6"/>
+      <c r="C170" s="8"/>
+      <c r="D170" s="8"/>
+    </row>
+    <row r="171" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A171" s="5"/>
+      <c r="B171" s="6"/>
+      <c r="C171" s="8"/>
+      <c r="D171" s="8"/>
+    </row>
+    <row r="172" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A172" s="5"/>
+      <c r="B172" s="6"/>
+      <c r="C172" s="8"/>
+      <c r="D172" s="8"/>
+    </row>
+    <row r="173" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A173" s="5"/>
+      <c r="B173" s="6"/>
+      <c r="C173" s="8"/>
+      <c r="D173" s="8"/>
+    </row>
+    <row r="174" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A174" s="5"/>
+      <c r="B174" s="6"/>
+      <c r="C174" s="8"/>
+      <c r="D174" s="8"/>
+    </row>
+    <row r="175" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="5"/>
+      <c r="B175" s="6"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="8"/>
+    </row>
+    <row r="176" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="5"/>
+      <c r="B176" s="6"/>
+      <c r="C176" s="8"/>
+      <c r="D176" s="8"/>
+    </row>
+    <row r="177" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="5"/>
+      <c r="B177" s="6"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="8"/>
+    </row>
+    <row r="178" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="5"/>
+      <c r="B178" s="6"/>
+      <c r="C178" s="8"/>
+      <c r="D178" s="8"/>
+    </row>
+    <row r="179" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="5"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="8"/>
+      <c r="D179" s="8"/>
+    </row>
+    <row r="180" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A180" s="5"/>
+      <c r="B180" s="6"/>
+      <c r="C180" s="8"/>
+      <c r="D180" s="8"/>
+    </row>
+    <row r="181" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A181" s="5"/>
+      <c r="B181" s="6"/>
+      <c r="C181" s="8"/>
+      <c r="D181" s="8"/>
+    </row>
+    <row r="182" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A182" s="5"/>
+      <c r="B182" s="6"/>
+      <c r="C182" s="8"/>
+      <c r="D182" s="8"/>
+    </row>
+    <row r="183" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A183" s="5"/>
+      <c r="B183" s="6"/>
+      <c r="C183" s="8"/>
+      <c r="D183" s="8"/>
+    </row>
+    <row r="184" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A184" s="5"/>
+      <c r="B184" s="6"/>
+      <c r="C184" s="8"/>
+      <c r="D184" s="8"/>
+    </row>
+    <row r="185" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A185" s="5"/>
+      <c r="B185" s="6"/>
+      <c r="C185" s="8"/>
+      <c r="D185" s="8"/>
+    </row>
+    <row r="186" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A186" s="5"/>
+      <c r="B186" s="6"/>
+      <c r="C186" s="8"/>
+      <c r="D186" s="8"/>
+    </row>
+    <row r="187" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A187" s="5"/>
+      <c r="B187" s="6"/>
+      <c r="C187" s="8"/>
+      <c r="D187" s="8"/>
+    </row>
+    <row r="188" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A188" s="5"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="8"/>
+      <c r="D188" s="8"/>
+    </row>
+    <row r="189" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A189" s="5"/>
+      <c r="B189" s="6"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="8"/>
+    </row>
+    <row r="190" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A190" s="5"/>
+      <c r="B190" s="6"/>
+      <c r="C190" s="8"/>
+      <c r="D190" s="8"/>
     </row>
     <row r="191" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="2"/>

--- a/assets/xlsx/Re Testing.xlsx
+++ b/assets/xlsx/Re Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMG\Documents\GITHUB\automationtestingjudges\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB3B5D6-6F4E-4AAA-ADE0-A7738BA7CA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD425729-8D50-4266-9A76-FDDEA582B042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>No</t>
   </si>
@@ -32,84 +32,6 @@
   </si>
   <si>
     <t>Context</t>
-  </si>
-  <si>
-    <t>Voicebot Botika dapat diintegrasikan di media atau platform apa pun selama platform tersebut mendukung fitur voicebot atau komunikasi suara.
-Integrasi bisa dilakukan melalui API atau gateway, baik untuk sistem telephony (seperti SIP dan softphone), platform digital (seperti WhatsApp Call, WebRTC, atau mobile app), maupun sistem bisnis internal seperti CRM atau ERP.
-Dengan fleksibilitas ini, voicebot dapat beroperasi di berbagai lingkungan sesuai kebutuhan pengguna.</t>
-  </si>
-  <si>
-    <t>Terdapat detail repot sbb pada dashboard voicebotika
-Outbound analytic:
-- start date
-- end date
-- call type
-- Total Campaign
-- Total call
-- Campaign performance
-- Succes Rate
--Succesfull call
-- Failed call
-- Outbound Call Performance
-- Average Call Duration
-- Total Call Duration
-- Daily outbound call volume
-Custom Analytics
-- start date
-- end date
-- call type
-- Custom Analytic Summary
-- Total Events
-- Top Categories 
-- Top Keys
-- Top Values
-- Custom Analytic Trends
-- Custom Analytic Events 
-https://pasteboard.co/fSQDVOa7BiSF.jpg 
-https://pasteboard.co/YQXISbPWV5Zu.jpg 
-Voicebotika sudah mendukung Open API Analytics yang mencakup:
-- Daily Analytics (jumlah kampanye, penerima, panggilan sukses/gagal, dan durasi).
-- Custom Events (kategori, key, value, agent, dan call ID).
-- Custom Summary (total event, top kategori, key, dan value).
-API ini membantu memantau performa kampanye dan insight perilaku pengguna secara real-time maupun historis.</t>
-  </si>
-  <si>
-    <t>Bisa, namun memerlukan custom khusus.
-Voicebot dapat dikembangkan untuk menyimpan data pelanggan dan jadwal pembayaran, termasuk mencatat status interaksi dan informasi penting lainnya.
-Melalui penyesuaian ini, data dapat diatur menggunakan kategori atau tagging agar mudah digunakan untuk pelaporan dan analisis lanjutan.</t>
-  </si>
-  <si>
-    <t>Hal tersebut bisa dilakukan, karena Botika sudah menggunakan teknologi Agentic AI yang mampu memahami konteks percakapan dan mengeksekusi tindakan secara proaktif.
-Secara teknis, voicebot dapat diintegrasikan dengan sistem pembayaran pihak ketiga (payment gateway) untuk mendukung proses seperti pemesanan dan pembayaran melalui percakapan suara.
-Namun, implementasi semacam ini belum efisien dari sisi user experience dan keamanan (security), karena proses autentikasi dan verifikasi pembayaran lebih optimal dilakukan melalui kanal dengan antarmuka visual.
-Oleh karena itu, penerapan fitur ini belum efisien untuk dilakukan dalam skenario voice interaction saat ini.</t>
-  </si>
-  <si>
-    <t>Hal tersebut sudah tersedia. Bahkan, jika ada kebutuhan untuk open API, fitur tersebut juga sudah disiapkan dan bisa diintegrasikan sesuai kebutuhan sistem kamu.
-Kalau kamu ingin tahu lebih detail soal implementasinya, kamu bisa langsung hubungi tim support Botika di support@botika.online
-.</t>
-  </si>
-  <si>
-    <t>Jumlah agent bergantung pada kompleksitas journey.
-Semakin kompleks alur, semakin banyak agent yang dibutuhkan.
-Contohnya, jika 1 menu memiliki 10 sub-menu, maka untuk 3 menu dibutuhkan minimal 3 agent. Namun jumlah ini tetap menyesuaikan tingkat kompleksitas dan fitur seperti eskalasi otomatis.
-Selain itu, juga terdapat fitur eskalasi otomatis ke agent manusia ketika voicebot tidak dapat menangani percakapan tertentu.</t>
-  </si>
-  <si>
-    <t>Hal tersebut bisa dilakukan, dan Voicebotika juga telah menyediakan Open API untuk mendukung integrasi dengan sistem eksternal.
-Selama API milik client memiliki endpoint dan dokumentasi yang sesuai, proses integrasi dapat dilakukan dengan penyesuaian teknis agar kedua sistem dapat saling berkomunikasi dengan baik, misalnya untuk verifikasi data, sinkronisasi informasi, atau eksekusi fungsi tertentu.</t>
-  </si>
-  <si>
-    <t>Transkrip call sudah tersedia pada fitur broadcast call di voicebotika. client dapat mengaskes transkrip panggilan antara agent dan pengguna. perlu diperhatikan, yang ditampilkan adalah transkrip call bukan chat console.</t>
-  </si>
-  <si>
-    <t>Fitur ini tersedia untuk mempermudah pengguna dalam menduplikasi sebuah agent. Proses cloning agent kini dapat dilakukan langsung oleh user yang memegang credential akun dashboard (PIC). Jadi, jika Anda perlu mengatur banyak skenario menggunakan satu persona agent yang sama, Anda dapat melakukannya secara mandiri melalui dashboard.</t>
-  </si>
-  <si>
-    <t>Fitur ini dapat dilakukan dengan penyesuaian pada Journey dan persona agent. Voicebot dapat memberikan interaksi dan penawaran yang personalized berdasarkan kondisi atau respons pengguna, sehingga skenario percakapan dapat disesuaikan untuk berbagai kebutuhan.</t>
-  </si>
-  <si>
-    <t>Voicebotika menyimpan transkrip dan hasil dalam bentuk summary, sehingga pengguna dapat melihat seluruh percakapan sekaligus output akhirnya, memudahkan analisis dan evaluasi performa agent.</t>
   </si>
   <si>
     <t>Terkait persona dan kompleksitas Voicebot, semua dapat diatur melalui dashboard Voicebot dengan metode prompting, menyesuaikan persona dan flow berdasarkan user journey. Dengan cara ini, skenario percakapan bisa dibuat untuk satu agent maupun lebih, termasuk penyesuaian alur dan nada ucapan per skenario. Misalnya, di awal percakapan Voicebotika bisa melakukan profiling untuk mengetahui apakah pengguna orang tua atau anak muda, sehingga alur dan nada ucapannya dapat disesuaikan dengan karakteristik pengguna tersebut.</t>
@@ -127,52 +49,9 @@
     <t>KB Platform V3</t>
   </si>
   <si>
-    <t>Bagaimana cara registrasi akun Omnibotika V2?</t>
-  </si>
-  <si>
-    <t>Untuk mendaftar layanan Botika dan mulai menggunakan produk seperti Omnibotika, Anda dapat mengikuti langkah-langkah berikut:
-1) Kunjungi Website Botika:
-Buka situs resmi Botika di https://botika.online/ untuk melihat berbagai produk dan layanan yang tersedia.
-2) Hubungi Tim Botika:
-Kirim email ke galuh@botika.online untuk mendapatkan informasi lebih lanjut mengenai pendaftaran dan cara memulai layanan yang Anda minati.
-3) Ikuti Instruksi Pendaftaran:
-Tim Botika akan memberikan panduan mengenai langkah-langkah pendaftaran, termasuk informasi yang perlu Anda siapkan.
-Jika Anda memiliki pertanyaan lebih lanjut atau membutuhkan bantuan selama proses pendaftaran, jangan ragu untuk menghubungi tim Botika.
-Selamat mencoba, dan semoga bisnis Anda semakin sukses!</t>
-  </si>
-  <si>
     <t>Untuk membuat bot dengan Omnibotika, biasanya prosesnya cukup fleksibel. Kamu bisa mendapatkan panduan lengkap untuk membuat dan menyesuaikan chatbot sesuai kebutuhan bisnismu. Omnibotika menyediakan opsi untuk membuat bot dari awal atau menyesuaikan bot yang sudah ada agar sesuai dengan kebutuhan spesifikmu.
 Jika kamu memerlukan panduan langkah atau bantuan lebih lanjut dalam proses pembuatan dan penyesuaian bot, Anda bisa melihat dokumentasi pada link https://docs.google.com/document/d/1O-ci1sM10-HirrK7gN3xHltUzfk_MoRbnDewwqkfTBk/edit?usp=drive_link. 
 Semoga sukses dengan pembuatan chatbot-mu!</t>
-  </si>
-  <si>
-    <t>Apakah ada paket Chatbot Gen AI?</t>
-  </si>
-  <si>
-    <t>Tentu! Chatbot Gen AI Profesional dirancang khusus untuk perusahaan besar yang menangani volume pelanggan tinggi dan membutuhkan sistem layanan otomatis yang cepat serta responsif.
-Paket ini mendukung hingga 10.000 MAU (Monthly Active Users) dengan harga Rp15.000.000 per bulan, dan sudah termasuk bonus 5 lisensi Omnichannel by Botika untuk membantu tim Anda mengelola komunikasi pelanggan di berbagai channel dengan lebih efisien.
-Cocok untuk organisasi besar yang ingin meningkatkan kualitas interaksi pelanggan sambil menjaga produktivitas dan kecepatan layanan.</t>
-  </si>
-  <si>
-    <t>KB Pricelist Dan SLA Botika</t>
-  </si>
-  <si>
-    <t>Apa itu WhatsApp Business Call?</t>
-  </si>
-  <si>
-    <t>WhatsApp Business Call adalah fitur resmi dari Meta yang memungkinkan bisnis melakukan dan menerima panggilan suara langsung melalui akun WhatsApp Business API. Dengan layanan ini, perusahaan bisa berinteraksi dengan pelanggan lewat suara secara lebih cepat, efisien, dan profesional tanpa harus menggunakan pulsa telepon biasa. Di Botika, fitur ini juga bisa diintegrasikan dengan Voicebot AI, IVR, dan sistem call center agar proses komunikasi menjadi otomatis namun tetap terasa natural.</t>
-  </si>
-  <si>
-    <t>Apakah WhatsApp Business Call aman digunakan?</t>
-  </si>
-  <si>
-    <t>Sangat aman. Semua komunikasi melalui Botika dienkripsi end-to-end sesuai kebijakan Meta. Selain itu, setiap panggilan dicatat secara aman dan hanya bisa diakses oleh petugas berwenang. Server Botika juga dilindungi dengan sistem keamanan berlapis agar data pelanggan tetap terlindungi.</t>
-  </si>
-  <si>
-    <t>Apakah layanan ini bisa diintegrasikan dengan CRM perusahaan?</t>
-  </si>
-  <si>
-    <t>Bisa. Botika menyediakan integrasi API dan webhook untuk menghubungkan data panggilan dengan CRM, sistem tiket, atau platform customer service lainnya. Jadi, semua interaksi pelanggan—baik yang lewat chat maupun panggilan—bisa terekam otomatis dalam satu sistem.</t>
   </si>
   <si>
     <t>Bagaimana kalau pelanggan sedang dalam panggilan lain?</t>
@@ -181,91 +60,61 @@
     <t>Jika pelanggan sedang melakukan panggilan lain, sistem akan menandai panggilan sebagai “busy” dan menjadwalkan ulang secara otomatis beberapa menit kemudian. Hal ini memastikan tidak ada gangguan dan panggilan bisa tetap dilakukan di waktu terbaik.</t>
   </si>
   <si>
-    <t>Kalau WhatsApp saya diblokir, apakah layanan tetap bisa digunakan?</t>
-  </si>
-  <si>
-    <t>Tidak bisa. Jika nomor bisnis diblokir oleh Meta, seluruh aktivitas panggilan otomatis akan berhenti. Namun, hal ini jarang terjadi jika bisnis mematuhi kebijakan komunikasi WhatsApp Business API.</t>
-  </si>
-  <si>
-    <t>Nomor yang digunakan untuk nelpon itu nomor saya atau nomor perusahaan?</t>
-  </si>
-  <si>
-    <t>Nomor yang digunakan adalah nomor bisnis resmi perusahaan yang sudah diverifikasi. Jadi, pelanggan akan melihat panggilan berasal dari akun WhatsApp bisnis dengan identitas dan logo perusahaan Anda.</t>
-  </si>
-  <si>
-    <t>Kalau pelanggan membalas dengan chat setelah panggilan, apakah sistem bisa merespons?</t>
-  </si>
-  <si>
-    <t>Bisa. Sistem kami mendukung mode hybrid, artinya pelanggan bisa melanjutkan komunikasi lewat chat setelah panggilan, dan sistem tetap bisa menjawab otomatis atau meneruskan ke agen manusia bila dibutuhkan.</t>
-  </si>
-  <si>
-    <t>Apakah bisa menggunakan nomor luar negeri untuk WhatsApp Call?</t>
-  </si>
-  <si>
-    <t>Bisa, asalkan nomor tersebut aktif, terdaftar di WhatsApp Business, dan wilayahnya didukung oleh kebijakan Meta. Sistem otomatis akan memverifikasi status nomor sebelum memulai panggilan.</t>
-  </si>
-  <si>
-    <t>Bagaimana cara menghentikan layanan WhatsApp Call jika tidak ingin lanjut berlangganan?</t>
-  </si>
-  <si>
-    <t>Kamu bisa menghentikan layanan dengan menonaktifkan akun bisnis yang digunakan atau menghubungi tim support Botika untuk penghentian akses agar nomor tidak lagi melakukan panggilan otomatis.</t>
-  </si>
-  <si>
-    <t>Apakah ada pelatihan untuk tim saya setelah aktivasi layanan?</t>
-  </si>
-  <si>
-    <t>Ada. Tim Botika menyediakan sesi onboarding dan training agar tim Anda paham cara menggunakan dashboard, laporan, serta fitur otomatisasi panggilan.</t>
-  </si>
-  <si>
-    <t>Apakah sistem bisa menggabungkan WhatsApp Call dengan chatbot teks?</t>
-  </si>
-  <si>
-    <t>Bisa banget. Layanan Botika mendukung integrasi hybrid antara voicebot dan chatbot teks. Jadi, pelanggan bisa mulai dengan panggilan suara, lalu melanjutkan obrolan lewat chat tanpa kehilangan konteks percakapan.</t>
-  </si>
-  <si>
     <t>KB WA Call</t>
   </si>
   <si>
     <t>aku mau buat chatbot, berikan aku Dokumentasi Platform</t>
   </si>
   <si>
-    <t>Apa saja platform yang bisa diintegrasikan dengan voicebot Botika?</t>
-  </si>
-  <si>
-    <t>Apa saja metrics dan fitur analytics yang tersedia di dashboard voicebotika?</t>
-  </si>
-  <si>
-    <t>Apakah voicebot bisa menyimpan data pelanggan dan jadwal pembayaran untuk kebutuhan penagihan?</t>
-  </si>
-  <si>
-    <t>Apakah voicebot Botika sudah menggunakan Generative AI dan bisa terhubung ke payment gateway?</t>
-  </si>
-  <si>
-    <t>Apakah voicebot Botika sudah memiliki fitur sentiment analytics?</t>
-  </si>
-  <si>
-    <t>Berapa banyak agent yang dibutuhkan jika terdapat beberapa skenario voicebot?</t>
-  </si>
-  <si>
-    <t>Apakah platform ailoov bisa diintegrasikan dengan API milik client?</t>
-  </si>
-  <si>
-    <t>Apakah tersedia fitur transcript call untuk memantau percakapan antara agent dan user?</t>
-  </si>
-  <si>
-    <t>Apakah ada fitur cloning agent untuk menduplikasi agent dengan persona yang sama?</t>
-  </si>
-  <si>
-    <t>Apakah voicebot bisa memberikan promosi backup yang disesuaikan dengan kondisi user?</t>
-  </si>
-  <si>
-    <t>Apakah koreksi ucapan user bisa terekam di reporting voicebotika?</t>
-  </si>
-  <si>
     <t>Sejauh mana persona dan alur percakapan voicebot bisa dikustomisasi per skenario?</t>
   </si>
   <si>
-    <t>omnibotika v2</t>
+    <t>KB Omnibotika V2</t>
+  </si>
+  <si>
+    <t>Apa itu Voicebotika?</t>
+  </si>
+  <si>
+    <t>Voicebotika Apps adalah aplikasi yang tersedia dalam versi Android yang dirancang untuk penggunaan di smartphone, dan juga tersedia sebagai platform berbasis web yang dapat diakses melalui browser. Di dalamnya, tersedia teknologi Text-to-Speech (TTS) dan Speech-to-Text (STT), sedangkan fitur asisten virtual berbasis AI bernama Selena hanya tersedia di versi Android.
+Dengan TTS, Anda bisa mengubah teks menjadi suara yang terdengar alami. Dengan STT, Anda bisa mengubah rekaman suara menjadi teks yang mudah disalin, diunduh, atau dibagikan. Selena sendiri dapat merespons percakapan sehari-hari baik lewat suara maupun teks.
+Aplikasi ini bermanfaat untuk berbagai kebutuhan, seperti notifikasi kustom, pembacaan e-book, pembuatan nada dering unik, hingga pencatatan suara otomatis.</t>
+  </si>
+  <si>
+    <t>KB Voicebotika APP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapan avatar DHAI diperbarui agar tetap sesuai brand dan relevansi? 
+</t>
+  </si>
+  <si>
+    <t>Avatar Digital Human AI diperbarui secara berkala sesuai perubahan identitas merek, gaya komunikasi, atau tampilan perusahaan, agar tetap relevan dan selaras dengan citra perusahaan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagaimana pembaruan AI dilakukan untuk tingkatkan akurasi DHAI? 
+</t>
+  </si>
+  <si>
+    <t>Pelatihan Digital Human AI dilakukan dengan menambahkan data percakapan baru serta memperbaiki respons sistem. Model DHAI terus belajar untuk meningkatkan akurasi, memahami konteks, dan mengenali emosi pengguna. Proses pembaruan dilakukan secara berkala untuk memastikan performa avatar tetap optimal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagaimana perusahaan mengukur efektivitas penggunaan DHAI? 
+</t>
+  </si>
+  <si>
+    <t>Efektivitas Digital Human AI diukur melalui data yang tersedia di dashboard, antara lain jumlah interaksi, tingkat kepuasan pengguna, dan persentase pertanyaan yang dapat dijawab tanpa intervensi manusia. Informasi ini digunakan untuk menilai sejauh mana DHAI mampu mempercepat layanan dan meningkatkan kualitas pengalaman pengguna.</t>
+  </si>
+  <si>
+    <t>KB DHAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apakah kita bisa menyesuaian waktu respons Voicebot? 
+</t>
+  </si>
+  <si>
+    <t>Saat ini, Voicebot tidak bisa mengatur kecepatan jawaban secara manual. Waktu respons yang diterima pengguna dapat berbeda-beda tergantung beberapa faktor, seperti kualitas dan stabilitas koneksi internet, panjang pertanyaan, serta beban server saat itu. Dengan koneksi yang stabil, respons biasanya lebih cepat dan lancar, sedangkan jika jaringan lemah, jawaban bisa sedikit tertunda.</t>
+  </si>
+  <si>
+    <t>KB Voicebot</t>
   </si>
 </sst>
 </file>
@@ -715,102 +564,102 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="88" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
+      <c r="C3" s="9" t="s">
+        <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
+      <c r="D3" s="9" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
+      <c r="C4" s="9" t="s">
+        <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
+      <c r="D4" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="113" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="63" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -818,280 +667,136 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="5">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="5">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="372.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="5">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="5">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="5">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="5">
-        <v>18</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="88" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="5">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="5">
-        <v>20</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="63" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="5">
-        <v>21</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="5">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="5">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="5">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="5">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="5">
+      <c r="C10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="5">
+      <c r="D10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>15</v>
-      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="5"/>
